--- a/docs/business/Listado Completo de Parcelas y Pricing.xlsx
+++ b/docs/business/Listado Completo de Parcelas y Pricing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julia\Python_Juli\Barrio Stefani 2\docs\business\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2091A1AF-7FCC-41E4-A657-BD22431850E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F4351D-08CC-42C3-A5EA-BC11CE1363FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Listado Unificado de Parcelas" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="Original Lotes a Escriturar" sheetId="3" r:id="rId3"/>
     <sheet name="Original Resumen por Manzana AE" sheetId="4" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Listado Unificado de Parcelas'!$A$1:$W$352</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Original Lotes a Escriturar'!$A$2:$L$123</definedName>
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="234">
   <si>
     <t>N°</t>
   </si>
@@ -741,6 +744,9 @@
   <si>
     <t>TOTAL</t>
   </si>
+  <si>
+    <t>NO DISPONIBLE</t>
+  </si>
 </sst>
 </file>
 
@@ -1086,6 +1092,3068 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Listado Lotes"/>
+      <sheetName val="TASACIONES"/>
+      <sheetName val="Comparables"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="E3">
+            <v>230.52</v>
+          </cell>
+          <cell r="K3" t="str">
+            <v>1-1</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="E4">
+            <v>233.98</v>
+          </cell>
+          <cell r="K4" t="str">
+            <v>1-2</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="E5">
+            <v>233.98</v>
+          </cell>
+          <cell r="K5" t="str">
+            <v>1-3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="E6">
+            <v>233.98</v>
+          </cell>
+          <cell r="K6" t="str">
+            <v>1-4</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="E7">
+            <v>233.98</v>
+          </cell>
+          <cell r="K7" t="str">
+            <v>1-5</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="E8">
+            <v>233.98</v>
+          </cell>
+          <cell r="K8" t="str">
+            <v>1-6</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="E9">
+            <v>229.5</v>
+          </cell>
+          <cell r="K9" t="str">
+            <v>1-7</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="E10">
+            <v>398.26</v>
+          </cell>
+          <cell r="K10" t="str">
+            <v>1-8</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="E11">
+            <v>398.26</v>
+          </cell>
+          <cell r="K11" t="str">
+            <v>1-9</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="E12">
+            <v>398.26</v>
+          </cell>
+          <cell r="K12" t="str">
+            <v>1-10</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="E13">
+            <v>398.26</v>
+          </cell>
+          <cell r="K13" t="str">
+            <v>1-11</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="E14">
+            <v>398.26</v>
+          </cell>
+          <cell r="K14" t="str">
+            <v>1-12</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="E15">
+            <v>398.26</v>
+          </cell>
+          <cell r="K15" t="str">
+            <v>1-13</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="E16">
+            <v>398.26</v>
+          </cell>
+          <cell r="K16" t="str">
+            <v>1-14</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="E17">
+            <v>398.26</v>
+          </cell>
+          <cell r="K17" t="str">
+            <v>1-15</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="E18">
+            <v>229.5</v>
+          </cell>
+          <cell r="K18" t="str">
+            <v>1-16</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19">
+            <v>233.98</v>
+          </cell>
+          <cell r="K19" t="str">
+            <v>1-17</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="E20">
+            <v>233.98</v>
+          </cell>
+          <cell r="K20" t="str">
+            <v>1-18</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21">
+            <v>233.98</v>
+          </cell>
+          <cell r="K21" t="str">
+            <v>1-19</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="E22">
+            <v>233.98</v>
+          </cell>
+          <cell r="K22" t="str">
+            <v>1-20</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="E23">
+            <v>233.98</v>
+          </cell>
+          <cell r="K23" t="str">
+            <v>1-21</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="E24">
+            <v>230.52</v>
+          </cell>
+          <cell r="K24" t="str">
+            <v>1-22</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="E25">
+            <v>235</v>
+          </cell>
+          <cell r="K25" t="str">
+            <v>1-23</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="E26">
+            <v>399.15</v>
+          </cell>
+          <cell r="K26" t="str">
+            <v>1-24</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="E27">
+            <v>399.15</v>
+          </cell>
+          <cell r="K27" t="str">
+            <v>1-25</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="E28">
+            <v>399.15</v>
+          </cell>
+          <cell r="K28" t="str">
+            <v>1-26</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="E29">
+            <v>399.15</v>
+          </cell>
+          <cell r="K29" t="str">
+            <v>1-27</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="E30">
+            <v>399.15</v>
+          </cell>
+          <cell r="K30" t="str">
+            <v>1-28</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="E31">
+            <v>399.15</v>
+          </cell>
+          <cell r="K31" t="str">
+            <v>1-29</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="E32">
+            <v>399.15</v>
+          </cell>
+          <cell r="K32" t="str">
+            <v>1-30</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="E33">
+            <v>399.15</v>
+          </cell>
+          <cell r="K33" t="str">
+            <v>1-31</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="E34">
+            <v>235</v>
+          </cell>
+          <cell r="K34" t="str">
+            <v>1-32</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="E35">
+            <v>229.5</v>
+          </cell>
+          <cell r="K35" t="str">
+            <v>2-1</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="E36">
+            <v>233.98</v>
+          </cell>
+          <cell r="K36" t="str">
+            <v>2-2</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="E37">
+            <v>233.98</v>
+          </cell>
+          <cell r="K37" t="str">
+            <v>2-3</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="E38">
+            <v>233.98</v>
+          </cell>
+          <cell r="K38" t="str">
+            <v>2-4</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="E39">
+            <v>233.98</v>
+          </cell>
+          <cell r="K39" t="str">
+            <v>2-5</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="E40">
+            <v>229.5</v>
+          </cell>
+          <cell r="K40" t="str">
+            <v>2-6</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="E41">
+            <v>298.69</v>
+          </cell>
+          <cell r="K41" t="str">
+            <v>2-7</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="E42">
+            <v>298.69</v>
+          </cell>
+          <cell r="K42" t="str">
+            <v>2-8</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="E43">
+            <v>298.69</v>
+          </cell>
+          <cell r="K43" t="str">
+            <v>2-9</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="E44">
+            <v>298.69</v>
+          </cell>
+          <cell r="K44" t="str">
+            <v>2-10</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="E45">
+            <v>298.69</v>
+          </cell>
+          <cell r="K45" t="str">
+            <v>2-11</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="E46">
+            <v>298.69</v>
+          </cell>
+          <cell r="K46" t="str">
+            <v>2-12</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="E47">
+            <v>298.69</v>
+          </cell>
+          <cell r="K47" t="str">
+            <v>2-13</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="E48">
+            <v>298.69</v>
+          </cell>
+          <cell r="K48" t="str">
+            <v>2-14</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="E49">
+            <v>229.5</v>
+          </cell>
+          <cell r="K49" t="str">
+            <v>2-15</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="E50">
+            <v>233.98</v>
+          </cell>
+          <cell r="K50" t="str">
+            <v>2-16</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="E51">
+            <v>233.98</v>
+          </cell>
+          <cell r="K51" t="str">
+            <v>2-17</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="E52">
+            <v>233.98</v>
+          </cell>
+          <cell r="K52" t="str">
+            <v>2-18</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="E53">
+            <v>233.98</v>
+          </cell>
+          <cell r="K53" t="str">
+            <v>2-19</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="E54">
+            <v>229.5</v>
+          </cell>
+          <cell r="K54" t="str">
+            <v>2-20</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="E55">
+            <v>298.69</v>
+          </cell>
+          <cell r="K55" t="str">
+            <v>2-21</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="E56">
+            <v>298.69</v>
+          </cell>
+          <cell r="K56" t="str">
+            <v>2-22</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="E57">
+            <v>298.69</v>
+          </cell>
+          <cell r="K57" t="str">
+            <v>2-23</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="E58">
+            <v>298.69</v>
+          </cell>
+          <cell r="K58" t="str">
+            <v>2-24</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="E59">
+            <v>298.69</v>
+          </cell>
+          <cell r="K59" t="str">
+            <v>2-25</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="E60">
+            <v>298.69</v>
+          </cell>
+          <cell r="K60" t="str">
+            <v>2-26</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="E61">
+            <v>298.69</v>
+          </cell>
+          <cell r="K61" t="str">
+            <v>2-27</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="E62">
+            <v>298.69</v>
+          </cell>
+          <cell r="K62" t="str">
+            <v>2-28</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="E63">
+            <v>229.5</v>
+          </cell>
+          <cell r="K63" t="str">
+            <v>3-1</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="E64">
+            <v>233.98</v>
+          </cell>
+          <cell r="K64" t="str">
+            <v>3-2</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="E65">
+            <v>233.98</v>
+          </cell>
+          <cell r="K65" t="str">
+            <v>3-3</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="E66">
+            <v>233.98</v>
+          </cell>
+          <cell r="K66" t="str">
+            <v>3-4</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="E67">
+            <v>233.98</v>
+          </cell>
+          <cell r="K67" t="str">
+            <v>3-5</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="E68">
+            <v>229.5</v>
+          </cell>
+          <cell r="K68" t="str">
+            <v>3-6</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="E69">
+            <v>298.69</v>
+          </cell>
+          <cell r="K69" t="str">
+            <v>3-7</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="E70">
+            <v>298.69</v>
+          </cell>
+          <cell r="K70" t="str">
+            <v>3-8</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="E71">
+            <v>298.69</v>
+          </cell>
+          <cell r="K71" t="str">
+            <v>3-9</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="E72">
+            <v>298.69</v>
+          </cell>
+          <cell r="K72" t="str">
+            <v>3-10</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="E73">
+            <v>298.69</v>
+          </cell>
+          <cell r="K73" t="str">
+            <v>3-11</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="E74">
+            <v>298.69</v>
+          </cell>
+          <cell r="K74" t="str">
+            <v>3-12</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="E75">
+            <v>298.69</v>
+          </cell>
+          <cell r="K75" t="str">
+            <v>3-13</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="E76">
+            <v>298.69</v>
+          </cell>
+          <cell r="K76" t="str">
+            <v>3-14</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="E77">
+            <v>229.5</v>
+          </cell>
+          <cell r="K77" t="str">
+            <v>3-15</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="E78">
+            <v>233.98</v>
+          </cell>
+          <cell r="K78" t="str">
+            <v>3-16</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="E79">
+            <v>233.98</v>
+          </cell>
+          <cell r="K79" t="str">
+            <v>3-17</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="E80">
+            <v>233.98</v>
+          </cell>
+          <cell r="K80" t="str">
+            <v>3-18</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="E81">
+            <v>233.98</v>
+          </cell>
+          <cell r="K81" t="str">
+            <v>3-19</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="E82">
+            <v>229.5</v>
+          </cell>
+          <cell r="K82" t="str">
+            <v>3-20</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="E83">
+            <v>298.69</v>
+          </cell>
+          <cell r="K83" t="str">
+            <v>3-21</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="E84">
+            <v>298.69</v>
+          </cell>
+          <cell r="K84" t="str">
+            <v>3-22</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="E85">
+            <v>298.69</v>
+          </cell>
+          <cell r="K85" t="str">
+            <v>3-23</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="E86">
+            <v>298.69</v>
+          </cell>
+          <cell r="K86" t="str">
+            <v>3-24</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="E87">
+            <v>298.69</v>
+          </cell>
+          <cell r="K87" t="str">
+            <v>3-25</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="E88">
+            <v>298.69</v>
+          </cell>
+          <cell r="K88" t="str">
+            <v>3-26</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="E89">
+            <v>298.69</v>
+          </cell>
+          <cell r="K89" t="str">
+            <v>3-27</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="E90">
+            <v>298.69</v>
+          </cell>
+          <cell r="K90" t="str">
+            <v>3-28</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="E91">
+            <v>230.52</v>
+          </cell>
+          <cell r="K91" t="str">
+            <v>31-1</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="E92">
+            <v>233.98</v>
+          </cell>
+          <cell r="K92" t="str">
+            <v>31-2</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="E93">
+            <v>233.98</v>
+          </cell>
+          <cell r="K93" t="str">
+            <v>31-3</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="E94">
+            <v>233.98</v>
+          </cell>
+          <cell r="K94" t="str">
+            <v>31-4</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="E95">
+            <v>233.98</v>
+          </cell>
+          <cell r="K95" t="str">
+            <v>31-5</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="E96">
+            <v>233.98</v>
+          </cell>
+          <cell r="K96" t="str">
+            <v>31-6</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="E97">
+            <v>229.5</v>
+          </cell>
+          <cell r="K97" t="str">
+            <v>31-7</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="E98">
+            <v>398.26</v>
+          </cell>
+          <cell r="K98" t="str">
+            <v>31-8</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="E99">
+            <v>398.26</v>
+          </cell>
+          <cell r="K99" t="str">
+            <v>31-9</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="E100">
+            <v>398.26</v>
+          </cell>
+          <cell r="K100" t="str">
+            <v>31-10</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="E101">
+            <v>398.26</v>
+          </cell>
+          <cell r="K101" t="str">
+            <v>31-11</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="E102">
+            <v>398.26</v>
+          </cell>
+          <cell r="K102" t="str">
+            <v>31-12</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="E103">
+            <v>398.26</v>
+          </cell>
+          <cell r="K103" t="str">
+            <v>31-13</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="E104">
+            <v>398.26</v>
+          </cell>
+          <cell r="K104" t="str">
+            <v>31-14</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="E105">
+            <v>398.26</v>
+          </cell>
+          <cell r="K105" t="str">
+            <v>31-15</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="E106">
+            <v>229.5</v>
+          </cell>
+          <cell r="K106" t="str">
+            <v>31-16</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="E107">
+            <v>233.98</v>
+          </cell>
+          <cell r="K107" t="str">
+            <v>31-17</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="E108">
+            <v>233.98</v>
+          </cell>
+          <cell r="K108" t="str">
+            <v>31-18</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="E109">
+            <v>233.98</v>
+          </cell>
+          <cell r="K109" t="str">
+            <v>31-19</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="E110">
+            <v>233.98</v>
+          </cell>
+          <cell r="K110" t="str">
+            <v>31-20</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="E111">
+            <v>233.98</v>
+          </cell>
+          <cell r="K111" t="str">
+            <v>31-21</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="E112">
+            <v>212.94</v>
+          </cell>
+          <cell r="K112" t="str">
+            <v>31-22</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="E113">
+            <v>235</v>
+          </cell>
+          <cell r="K113" t="str">
+            <v>31-23</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="E114">
+            <v>399.15</v>
+          </cell>
+          <cell r="K114" t="str">
+            <v>31-24</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="E115">
+            <v>399.15</v>
+          </cell>
+          <cell r="K115" t="str">
+            <v>31-25</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="E116">
+            <v>399.15</v>
+          </cell>
+          <cell r="K116" t="str">
+            <v>31-26</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="E117">
+            <v>399.15</v>
+          </cell>
+          <cell r="K117" t="str">
+            <v>31-27</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="E118">
+            <v>399.15</v>
+          </cell>
+          <cell r="K118" t="str">
+            <v>31-28</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="E119">
+            <v>399.15</v>
+          </cell>
+          <cell r="K119" t="str">
+            <v>31-29</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="E120">
+            <v>399.15</v>
+          </cell>
+          <cell r="K120" t="str">
+            <v>31-30</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="E121">
+            <v>399.15</v>
+          </cell>
+          <cell r="K121" t="str">
+            <v>31-31</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="E122">
+            <v>235</v>
+          </cell>
+          <cell r="K122" t="str">
+            <v>31-32</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="E123">
+            <v>229.5</v>
+          </cell>
+          <cell r="K123" t="str">
+            <v>32-1</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="E124">
+            <v>233.98</v>
+          </cell>
+          <cell r="K124" t="str">
+            <v>32-2</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="E125">
+            <v>233.98</v>
+          </cell>
+          <cell r="K125" t="str">
+            <v>32-3</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="E126">
+            <v>233.98</v>
+          </cell>
+          <cell r="K126" t="str">
+            <v>32-4</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="E127">
+            <v>233.98</v>
+          </cell>
+          <cell r="K127" t="str">
+            <v>32-5</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="E128">
+            <v>229.5</v>
+          </cell>
+          <cell r="K128" t="str">
+            <v>32-6</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="E129">
+            <v>298.69</v>
+          </cell>
+          <cell r="K129" t="str">
+            <v>32-7</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="E130">
+            <v>298.69</v>
+          </cell>
+          <cell r="K130" t="str">
+            <v>32-8</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="E131">
+            <v>298.69</v>
+          </cell>
+          <cell r="K131" t="str">
+            <v>32-9</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="E132">
+            <v>298.69</v>
+          </cell>
+          <cell r="K132" t="str">
+            <v>32-10</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="E133">
+            <v>298.69</v>
+          </cell>
+          <cell r="K133" t="str">
+            <v>32-11</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="E134">
+            <v>298.69</v>
+          </cell>
+          <cell r="K134" t="str">
+            <v>32-12</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="E135">
+            <v>298.69</v>
+          </cell>
+          <cell r="K135" t="str">
+            <v>32-13</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="E136">
+            <v>298.69</v>
+          </cell>
+          <cell r="K136" t="str">
+            <v>32-14</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="E137">
+            <v>229.5</v>
+          </cell>
+          <cell r="K137" t="str">
+            <v>32-15</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="E138">
+            <v>233.98</v>
+          </cell>
+          <cell r="K138" t="str">
+            <v>32-16</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="E139">
+            <v>233.98</v>
+          </cell>
+          <cell r="K139" t="str">
+            <v>32-17</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="E140">
+            <v>233.98</v>
+          </cell>
+          <cell r="K140" t="str">
+            <v>32-18</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="E141">
+            <v>233.98</v>
+          </cell>
+          <cell r="K141" t="str">
+            <v>32-19</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="E142">
+            <v>229.5</v>
+          </cell>
+          <cell r="K142" t="str">
+            <v>32-20</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="E143">
+            <v>298.69</v>
+          </cell>
+          <cell r="K143" t="str">
+            <v>32-21</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="E144">
+            <v>298.69</v>
+          </cell>
+          <cell r="K144" t="str">
+            <v>32-22</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="E145">
+            <v>298.69</v>
+          </cell>
+          <cell r="K145" t="str">
+            <v>32-23</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="E146">
+            <v>298.69</v>
+          </cell>
+          <cell r="K146" t="str">
+            <v>32-24</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="E147">
+            <v>298.69</v>
+          </cell>
+          <cell r="K147" t="str">
+            <v>32-25</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="E148">
+            <v>298.69</v>
+          </cell>
+          <cell r="K148" t="str">
+            <v>32-26</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="E149">
+            <v>298.69</v>
+          </cell>
+          <cell r="K149" t="str">
+            <v>32-27</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="E150">
+            <v>298.69</v>
+          </cell>
+          <cell r="K150" t="str">
+            <v>32-28</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="E151">
+            <v>229.5</v>
+          </cell>
+          <cell r="K151" t="str">
+            <v>33-1</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="E152">
+            <v>233.98</v>
+          </cell>
+          <cell r="K152" t="str">
+            <v>33-2</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="E153">
+            <v>233.98</v>
+          </cell>
+          <cell r="K153" t="str">
+            <v>33-3</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="E154">
+            <v>233.98</v>
+          </cell>
+          <cell r="K154" t="str">
+            <v>33-4</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="E155">
+            <v>233.98</v>
+          </cell>
+          <cell r="K155" t="str">
+            <v>33-5</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="E156">
+            <v>229.5</v>
+          </cell>
+          <cell r="K156" t="str">
+            <v>33-6</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="E157">
+            <v>298.69</v>
+          </cell>
+          <cell r="K157" t="str">
+            <v>33-7</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="E158">
+            <v>298.69</v>
+          </cell>
+          <cell r="K158" t="str">
+            <v>33-8</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="E159">
+            <v>298.69</v>
+          </cell>
+          <cell r="K159" t="str">
+            <v>33-9</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="E160">
+            <v>298.69</v>
+          </cell>
+          <cell r="K160" t="str">
+            <v>33-10</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="E161">
+            <v>298.69</v>
+          </cell>
+          <cell r="K161" t="str">
+            <v>33-11</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="E162">
+            <v>298.69</v>
+          </cell>
+          <cell r="K162" t="str">
+            <v>33-12</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="E163">
+            <v>298.69</v>
+          </cell>
+          <cell r="K163" t="str">
+            <v>33-13</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="E164">
+            <v>298.69</v>
+          </cell>
+          <cell r="K164" t="str">
+            <v>33-14</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="E165">
+            <v>213.22</v>
+          </cell>
+          <cell r="K165" t="str">
+            <v>33-15</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="E166">
+            <v>233.98</v>
+          </cell>
+          <cell r="K166" t="str">
+            <v>33-16</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="E167">
+            <v>233.98</v>
+          </cell>
+          <cell r="K167" t="str">
+            <v>33-17</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="E168">
+            <v>233.98</v>
+          </cell>
+          <cell r="K168" t="str">
+            <v>33-18</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="E169">
+            <v>233.98</v>
+          </cell>
+          <cell r="K169" t="str">
+            <v>33-19</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="E170">
+            <v>229.5</v>
+          </cell>
+          <cell r="K170" t="str">
+            <v>33-20</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="E171">
+            <v>298.69</v>
+          </cell>
+          <cell r="K171" t="str">
+            <v>33-21</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="E172">
+            <v>298.69</v>
+          </cell>
+          <cell r="K172" t="str">
+            <v>33-22</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="E173">
+            <v>298.69</v>
+          </cell>
+          <cell r="K173" t="str">
+            <v>33-23</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="E174">
+            <v>298.69</v>
+          </cell>
+          <cell r="K174" t="str">
+            <v>33-24</v>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="E175">
+            <v>298.69</v>
+          </cell>
+          <cell r="K175" t="str">
+            <v>33-25</v>
+          </cell>
+        </row>
+        <row r="176">
+          <cell r="E176">
+            <v>298.69</v>
+          </cell>
+          <cell r="K176" t="str">
+            <v>33-26</v>
+          </cell>
+        </row>
+        <row r="177">
+          <cell r="E177">
+            <v>298.69</v>
+          </cell>
+          <cell r="K177" t="str">
+            <v>33-27</v>
+          </cell>
+        </row>
+        <row r="178">
+          <cell r="E178">
+            <v>298.69</v>
+          </cell>
+          <cell r="K178" t="str">
+            <v>33-28</v>
+          </cell>
+        </row>
+        <row r="179">
+          <cell r="E179">
+            <v>214.24</v>
+          </cell>
+          <cell r="K179" t="str">
+            <v>94-1</v>
+          </cell>
+        </row>
+        <row r="180">
+          <cell r="E180">
+            <v>233.98</v>
+          </cell>
+          <cell r="K180" t="str">
+            <v>94-2</v>
+          </cell>
+        </row>
+        <row r="181">
+          <cell r="E181">
+            <v>233.98</v>
+          </cell>
+          <cell r="K181" t="str">
+            <v>94-3</v>
+          </cell>
+        </row>
+        <row r="182">
+          <cell r="E182">
+            <v>233.98</v>
+          </cell>
+          <cell r="K182" t="str">
+            <v>94-4</v>
+          </cell>
+        </row>
+        <row r="183">
+          <cell r="E183">
+            <v>233.98</v>
+          </cell>
+          <cell r="K183" t="str">
+            <v>94-5</v>
+          </cell>
+        </row>
+        <row r="184">
+          <cell r="E184">
+            <v>233.98</v>
+          </cell>
+          <cell r="K184" t="str">
+            <v>94-6</v>
+          </cell>
+        </row>
+        <row r="185">
+          <cell r="E185">
+            <v>229.5</v>
+          </cell>
+          <cell r="K185" t="str">
+            <v>94-7</v>
+          </cell>
+        </row>
+        <row r="186">
+          <cell r="E186">
+            <v>398.26</v>
+          </cell>
+          <cell r="K186" t="str">
+            <v>94-8</v>
+          </cell>
+        </row>
+        <row r="187">
+          <cell r="E187">
+            <v>398.26</v>
+          </cell>
+          <cell r="K187" t="str">
+            <v>94-9</v>
+          </cell>
+        </row>
+        <row r="188">
+          <cell r="E188">
+            <v>398.26</v>
+          </cell>
+          <cell r="K188" t="str">
+            <v>94-10</v>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="E189">
+            <v>398.26</v>
+          </cell>
+          <cell r="K189" t="str">
+            <v>94-11</v>
+          </cell>
+        </row>
+        <row r="190">
+          <cell r="E190">
+            <v>398.26</v>
+          </cell>
+          <cell r="K190" t="str">
+            <v>94-12</v>
+          </cell>
+        </row>
+        <row r="191">
+          <cell r="E191">
+            <v>398.26</v>
+          </cell>
+          <cell r="K191" t="str">
+            <v>94-13</v>
+          </cell>
+        </row>
+        <row r="192">
+          <cell r="E192">
+            <v>398.26</v>
+          </cell>
+          <cell r="K192" t="str">
+            <v>94-14</v>
+          </cell>
+        </row>
+        <row r="193">
+          <cell r="E193">
+            <v>398.26</v>
+          </cell>
+          <cell r="K193" t="str">
+            <v>94-15</v>
+          </cell>
+        </row>
+        <row r="194">
+          <cell r="E194">
+            <v>229.5</v>
+          </cell>
+          <cell r="K194" t="str">
+            <v>94-16</v>
+          </cell>
+        </row>
+        <row r="195">
+          <cell r="E195">
+            <v>233.98</v>
+          </cell>
+          <cell r="K195" t="str">
+            <v>94-17</v>
+          </cell>
+        </row>
+        <row r="196">
+          <cell r="E196">
+            <v>233.98</v>
+          </cell>
+          <cell r="K196" t="str">
+            <v>94-18</v>
+          </cell>
+        </row>
+        <row r="197">
+          <cell r="E197">
+            <v>233.98</v>
+          </cell>
+          <cell r="K197" t="str">
+            <v>94-19</v>
+          </cell>
+        </row>
+        <row r="198">
+          <cell r="E198">
+            <v>233.98</v>
+          </cell>
+          <cell r="K198" t="str">
+            <v>94-20</v>
+          </cell>
+        </row>
+        <row r="199">
+          <cell r="E199">
+            <v>233.98</v>
+          </cell>
+          <cell r="K199" t="str">
+            <v>94-21</v>
+          </cell>
+        </row>
+        <row r="200">
+          <cell r="E200">
+            <v>230.52</v>
+          </cell>
+          <cell r="K200" t="str">
+            <v>94-22</v>
+          </cell>
+        </row>
+        <row r="201">
+          <cell r="E201">
+            <v>235</v>
+          </cell>
+          <cell r="K201" t="str">
+            <v>94-23</v>
+          </cell>
+        </row>
+        <row r="202">
+          <cell r="E202">
+            <v>399.15</v>
+          </cell>
+          <cell r="K202" t="str">
+            <v>94-24</v>
+          </cell>
+        </row>
+        <row r="203">
+          <cell r="E203">
+            <v>399.15</v>
+          </cell>
+          <cell r="K203" t="str">
+            <v>94-25</v>
+          </cell>
+        </row>
+        <row r="204">
+          <cell r="E204">
+            <v>399.15</v>
+          </cell>
+          <cell r="K204" t="str">
+            <v>94-26</v>
+          </cell>
+        </row>
+        <row r="205">
+          <cell r="E205">
+            <v>399.15</v>
+          </cell>
+          <cell r="K205" t="str">
+            <v>94-27</v>
+          </cell>
+        </row>
+        <row r="206">
+          <cell r="E206">
+            <v>399.15</v>
+          </cell>
+          <cell r="K206" t="str">
+            <v>94-28</v>
+          </cell>
+        </row>
+        <row r="207">
+          <cell r="E207">
+            <v>399.15</v>
+          </cell>
+          <cell r="K207" t="str">
+            <v>94-29</v>
+          </cell>
+        </row>
+        <row r="208">
+          <cell r="E208">
+            <v>399.15</v>
+          </cell>
+          <cell r="K208" t="str">
+            <v>94-30</v>
+          </cell>
+        </row>
+        <row r="209">
+          <cell r="E209">
+            <v>399.15</v>
+          </cell>
+          <cell r="K209" t="str">
+            <v>94-31</v>
+          </cell>
+        </row>
+        <row r="210">
+          <cell r="E210">
+            <v>235</v>
+          </cell>
+          <cell r="K210" t="str">
+            <v>94-32</v>
+          </cell>
+        </row>
+        <row r="211">
+          <cell r="E211">
+            <v>229.5</v>
+          </cell>
+          <cell r="K211" t="str">
+            <v>95-1</v>
+          </cell>
+        </row>
+        <row r="212">
+          <cell r="E212">
+            <v>233.98</v>
+          </cell>
+          <cell r="K212" t="str">
+            <v>95-2</v>
+          </cell>
+        </row>
+        <row r="213">
+          <cell r="E213">
+            <v>233.98</v>
+          </cell>
+          <cell r="K213" t="str">
+            <v>95-3</v>
+          </cell>
+        </row>
+        <row r="214">
+          <cell r="E214">
+            <v>233.98</v>
+          </cell>
+          <cell r="K214" t="str">
+            <v>95-4</v>
+          </cell>
+        </row>
+        <row r="215">
+          <cell r="E215">
+            <v>233.98</v>
+          </cell>
+          <cell r="K215" t="str">
+            <v>95-5</v>
+          </cell>
+        </row>
+        <row r="216">
+          <cell r="E216">
+            <v>229.5</v>
+          </cell>
+          <cell r="K216" t="str">
+            <v>95-6</v>
+          </cell>
+        </row>
+        <row r="217">
+          <cell r="E217">
+            <v>298.69</v>
+          </cell>
+          <cell r="K217" t="str">
+            <v>95-7</v>
+          </cell>
+        </row>
+        <row r="218">
+          <cell r="E218">
+            <v>298.69</v>
+          </cell>
+          <cell r="K218" t="str">
+            <v>95-8</v>
+          </cell>
+        </row>
+        <row r="219">
+          <cell r="E219">
+            <v>298.69</v>
+          </cell>
+          <cell r="K219" t="str">
+            <v>95-9</v>
+          </cell>
+        </row>
+        <row r="220">
+          <cell r="E220">
+            <v>298.69</v>
+          </cell>
+          <cell r="K220" t="str">
+            <v>95-10</v>
+          </cell>
+        </row>
+        <row r="221">
+          <cell r="E221">
+            <v>298.69</v>
+          </cell>
+          <cell r="K221" t="str">
+            <v>95-11</v>
+          </cell>
+        </row>
+        <row r="222">
+          <cell r="E222">
+            <v>298.69</v>
+          </cell>
+          <cell r="K222" t="str">
+            <v>95-12</v>
+          </cell>
+        </row>
+        <row r="223">
+          <cell r="E223">
+            <v>298.69</v>
+          </cell>
+          <cell r="K223" t="str">
+            <v>95-13</v>
+          </cell>
+        </row>
+        <row r="224">
+          <cell r="E224">
+            <v>298.69</v>
+          </cell>
+          <cell r="K224" t="str">
+            <v>95-14</v>
+          </cell>
+        </row>
+        <row r="225">
+          <cell r="E225">
+            <v>229.5</v>
+          </cell>
+          <cell r="K225" t="str">
+            <v>95-15</v>
+          </cell>
+        </row>
+        <row r="226">
+          <cell r="E226">
+            <v>233.98</v>
+          </cell>
+          <cell r="K226" t="str">
+            <v>95-16</v>
+          </cell>
+        </row>
+        <row r="227">
+          <cell r="E227">
+            <v>233.98</v>
+          </cell>
+          <cell r="K227" t="str">
+            <v>95-17</v>
+          </cell>
+        </row>
+        <row r="228">
+          <cell r="E228">
+            <v>233.98</v>
+          </cell>
+          <cell r="K228" t="str">
+            <v>95-18</v>
+          </cell>
+        </row>
+        <row r="229">
+          <cell r="E229">
+            <v>233.98</v>
+          </cell>
+          <cell r="K229" t="str">
+            <v>95-19</v>
+          </cell>
+        </row>
+        <row r="230">
+          <cell r="E230">
+            <v>229.5</v>
+          </cell>
+          <cell r="K230" t="str">
+            <v>95-20</v>
+          </cell>
+        </row>
+        <row r="231">
+          <cell r="E231">
+            <v>298.69</v>
+          </cell>
+          <cell r="K231" t="str">
+            <v>95-21</v>
+          </cell>
+        </row>
+        <row r="232">
+          <cell r="E232">
+            <v>298.69</v>
+          </cell>
+          <cell r="K232" t="str">
+            <v>95-22</v>
+          </cell>
+        </row>
+        <row r="233">
+          <cell r="E233">
+            <v>298.69</v>
+          </cell>
+          <cell r="K233" t="str">
+            <v>95-23</v>
+          </cell>
+        </row>
+        <row r="234">
+          <cell r="E234">
+            <v>298.69</v>
+          </cell>
+          <cell r="K234" t="str">
+            <v>95-24</v>
+          </cell>
+        </row>
+        <row r="235">
+          <cell r="E235">
+            <v>298.69</v>
+          </cell>
+          <cell r="K235" t="str">
+            <v>95-25</v>
+          </cell>
+        </row>
+        <row r="236">
+          <cell r="E236">
+            <v>298.69</v>
+          </cell>
+          <cell r="K236" t="str">
+            <v>95-26</v>
+          </cell>
+        </row>
+        <row r="237">
+          <cell r="E237">
+            <v>298.69</v>
+          </cell>
+          <cell r="K237" t="str">
+            <v>95-27</v>
+          </cell>
+        </row>
+        <row r="238">
+          <cell r="E238">
+            <v>298.69</v>
+          </cell>
+          <cell r="K238" t="str">
+            <v>95-28</v>
+          </cell>
+        </row>
+        <row r="239">
+          <cell r="E239">
+            <v>229.5</v>
+          </cell>
+          <cell r="K239" t="str">
+            <v>96-1</v>
+          </cell>
+        </row>
+        <row r="240">
+          <cell r="E240">
+            <v>233.98</v>
+          </cell>
+          <cell r="K240" t="str">
+            <v>96-2</v>
+          </cell>
+        </row>
+        <row r="241">
+          <cell r="E241">
+            <v>233.98</v>
+          </cell>
+          <cell r="K241" t="str">
+            <v>96-3</v>
+          </cell>
+        </row>
+        <row r="242">
+          <cell r="E242">
+            <v>0</v>
+          </cell>
+          <cell r="K242" t="str">
+            <v>96-</v>
+          </cell>
+        </row>
+        <row r="243">
+          <cell r="E243">
+            <v>0</v>
+          </cell>
+          <cell r="K243" t="str">
+            <v>96-</v>
+          </cell>
+        </row>
+        <row r="244">
+          <cell r="E244">
+            <v>0</v>
+          </cell>
+          <cell r="K244" t="str">
+            <v>96-</v>
+          </cell>
+        </row>
+        <row r="245">
+          <cell r="E245">
+            <v>0</v>
+          </cell>
+          <cell r="K245" t="str">
+            <v>96-</v>
+          </cell>
+        </row>
+        <row r="246">
+          <cell r="E246">
+            <v>0</v>
+          </cell>
+          <cell r="K246" t="str">
+            <v>96-</v>
+          </cell>
+        </row>
+        <row r="247">
+          <cell r="E247">
+            <v>0</v>
+          </cell>
+          <cell r="K247" t="str">
+            <v>96-</v>
+          </cell>
+        </row>
+        <row r="248">
+          <cell r="E248">
+            <v>0</v>
+          </cell>
+          <cell r="K248" t="str">
+            <v>96-</v>
+          </cell>
+        </row>
+        <row r="249">
+          <cell r="E249">
+            <v>0</v>
+          </cell>
+          <cell r="K249" t="str">
+            <v>96-</v>
+          </cell>
+        </row>
+        <row r="250">
+          <cell r="E250">
+            <v>298.69</v>
+          </cell>
+          <cell r="K250" t="str">
+            <v>96-12</v>
+          </cell>
+        </row>
+        <row r="251">
+          <cell r="E251">
+            <v>298.69</v>
+          </cell>
+          <cell r="K251" t="str">
+            <v>96-13</v>
+          </cell>
+        </row>
+        <row r="252">
+          <cell r="E252">
+            <v>298.69</v>
+          </cell>
+          <cell r="K252" t="str">
+            <v>96-14</v>
+          </cell>
+        </row>
+        <row r="253">
+          <cell r="E253">
+            <v>229.5</v>
+          </cell>
+          <cell r="K253" t="str">
+            <v>96-15</v>
+          </cell>
+        </row>
+        <row r="254">
+          <cell r="E254">
+            <v>233.98</v>
+          </cell>
+          <cell r="K254" t="str">
+            <v>96-16</v>
+          </cell>
+        </row>
+        <row r="255">
+          <cell r="E255">
+            <v>233.98</v>
+          </cell>
+          <cell r="K255" t="str">
+            <v>96-17</v>
+          </cell>
+        </row>
+        <row r="256">
+          <cell r="K256" t="str">
+            <v>96-</v>
+          </cell>
+        </row>
+        <row r="257">
+          <cell r="E257">
+            <v>233.98</v>
+          </cell>
+          <cell r="K257" t="str">
+            <v>96-19</v>
+          </cell>
+        </row>
+        <row r="258">
+          <cell r="E258">
+            <v>229.5</v>
+          </cell>
+          <cell r="K258" t="str">
+            <v>96-20</v>
+          </cell>
+        </row>
+        <row r="259">
+          <cell r="K259" t="str">
+            <v>96-</v>
+          </cell>
+        </row>
+        <row r="260">
+          <cell r="E260">
+            <v>298.69</v>
+          </cell>
+          <cell r="K260" t="str">
+            <v>96-22</v>
+          </cell>
+        </row>
+        <row r="261">
+          <cell r="E261">
+            <v>298.69</v>
+          </cell>
+          <cell r="K261" t="str">
+            <v>96-23</v>
+          </cell>
+        </row>
+        <row r="262">
+          <cell r="E262">
+            <v>298.69</v>
+          </cell>
+          <cell r="K262" t="str">
+            <v>96-24</v>
+          </cell>
+        </row>
+        <row r="263">
+          <cell r="E263">
+            <v>298.69</v>
+          </cell>
+          <cell r="K263" t="str">
+            <v>96-25</v>
+          </cell>
+        </row>
+        <row r="264">
+          <cell r="E264">
+            <v>298.69</v>
+          </cell>
+          <cell r="K264" t="str">
+            <v>96-26</v>
+          </cell>
+        </row>
+        <row r="265">
+          <cell r="E265">
+            <v>298.69</v>
+          </cell>
+          <cell r="K265" t="str">
+            <v>96-27</v>
+          </cell>
+        </row>
+        <row r="266">
+          <cell r="E266">
+            <v>298.69</v>
+          </cell>
+          <cell r="K266" t="str">
+            <v>96-28</v>
+          </cell>
+        </row>
+        <row r="267">
+          <cell r="K267" t="str">
+            <v>124-</v>
+          </cell>
+        </row>
+        <row r="268">
+          <cell r="K268" t="str">
+            <v>124-</v>
+          </cell>
+        </row>
+        <row r="269">
+          <cell r="K269" t="str">
+            <v>124-</v>
+          </cell>
+        </row>
+        <row r="270">
+          <cell r="K270" t="str">
+            <v>124-</v>
+          </cell>
+        </row>
+        <row r="271">
+          <cell r="K271" t="str">
+            <v>124-</v>
+          </cell>
+        </row>
+        <row r="272">
+          <cell r="E272">
+            <v>233.98</v>
+          </cell>
+          <cell r="K272" t="str">
+            <v>124-6</v>
+          </cell>
+        </row>
+        <row r="273">
+          <cell r="E273">
+            <v>229.5</v>
+          </cell>
+          <cell r="K273" t="str">
+            <v>124-7</v>
+          </cell>
+        </row>
+        <row r="274">
+          <cell r="E274">
+            <v>398.26</v>
+          </cell>
+          <cell r="K274" t="str">
+            <v>124-8</v>
+          </cell>
+        </row>
+        <row r="275">
+          <cell r="E275">
+            <v>398.26</v>
+          </cell>
+          <cell r="K275" t="str">
+            <v>124-9</v>
+          </cell>
+        </row>
+        <row r="276">
+          <cell r="E276">
+            <v>398.26</v>
+          </cell>
+          <cell r="K276" t="str">
+            <v>124-10</v>
+          </cell>
+        </row>
+        <row r="277">
+          <cell r="E277">
+            <v>398.26</v>
+          </cell>
+          <cell r="K277" t="str">
+            <v>124-11</v>
+          </cell>
+        </row>
+        <row r="278">
+          <cell r="E278">
+            <v>398.26</v>
+          </cell>
+          <cell r="K278" t="str">
+            <v>124-12</v>
+          </cell>
+        </row>
+        <row r="279">
+          <cell r="E279">
+            <v>398.26</v>
+          </cell>
+          <cell r="K279" t="str">
+            <v>124-13</v>
+          </cell>
+        </row>
+        <row r="280">
+          <cell r="E280">
+            <v>398.26</v>
+          </cell>
+          <cell r="K280" t="str">
+            <v>124-14</v>
+          </cell>
+        </row>
+        <row r="281">
+          <cell r="E281">
+            <v>398.26</v>
+          </cell>
+          <cell r="K281" t="str">
+            <v>124-15</v>
+          </cell>
+        </row>
+        <row r="282">
+          <cell r="E282">
+            <v>229.5</v>
+          </cell>
+          <cell r="K282" t="str">
+            <v>124-16</v>
+          </cell>
+        </row>
+        <row r="283">
+          <cell r="E283">
+            <v>233.98</v>
+          </cell>
+          <cell r="K283" t="str">
+            <v>124-17</v>
+          </cell>
+        </row>
+        <row r="284">
+          <cell r="E284">
+            <v>233.98</v>
+          </cell>
+          <cell r="K284" t="str">
+            <v>124-18</v>
+          </cell>
+        </row>
+        <row r="285">
+          <cell r="E285">
+            <v>233.98</v>
+          </cell>
+          <cell r="K285" t="str">
+            <v>124-19</v>
+          </cell>
+        </row>
+        <row r="286">
+          <cell r="E286">
+            <v>233.98</v>
+          </cell>
+          <cell r="K286" t="str">
+            <v>124-20</v>
+          </cell>
+        </row>
+        <row r="287">
+          <cell r="E287">
+            <v>233.98</v>
+          </cell>
+          <cell r="K287" t="str">
+            <v>124-21</v>
+          </cell>
+        </row>
+        <row r="288">
+          <cell r="E288">
+            <v>230.52</v>
+          </cell>
+          <cell r="K288" t="str">
+            <v>124-22</v>
+          </cell>
+        </row>
+        <row r="289">
+          <cell r="E289">
+            <v>235</v>
+          </cell>
+          <cell r="K289" t="str">
+            <v>124-23</v>
+          </cell>
+        </row>
+        <row r="290">
+          <cell r="E290">
+            <v>399.15</v>
+          </cell>
+          <cell r="K290" t="str">
+            <v>124-24</v>
+          </cell>
+        </row>
+        <row r="291">
+          <cell r="E291">
+            <v>399.15</v>
+          </cell>
+          <cell r="K291" t="str">
+            <v>124-25</v>
+          </cell>
+        </row>
+        <row r="292">
+          <cell r="E292">
+            <v>399.15</v>
+          </cell>
+          <cell r="K292" t="str">
+            <v>124-26</v>
+          </cell>
+        </row>
+        <row r="293">
+          <cell r="E293">
+            <v>399.15</v>
+          </cell>
+          <cell r="K293" t="str">
+            <v>124-27</v>
+          </cell>
+        </row>
+        <row r="294">
+          <cell r="E294">
+            <v>399.15</v>
+          </cell>
+          <cell r="K294" t="str">
+            <v>124-28</v>
+          </cell>
+        </row>
+        <row r="295">
+          <cell r="E295">
+            <v>399.15</v>
+          </cell>
+          <cell r="K295" t="str">
+            <v>124-29</v>
+          </cell>
+        </row>
+        <row r="296">
+          <cell r="E296">
+            <v>399.15</v>
+          </cell>
+          <cell r="K296" t="str">
+            <v>124-30</v>
+          </cell>
+        </row>
+        <row r="297">
+          <cell r="E297">
+            <v>399.15</v>
+          </cell>
+          <cell r="K297" t="str">
+            <v>124-31</v>
+          </cell>
+        </row>
+        <row r="298">
+          <cell r="K298" t="str">
+            <v>124-</v>
+          </cell>
+        </row>
+        <row r="299">
+          <cell r="E299">
+            <v>229.5</v>
+          </cell>
+          <cell r="K299" t="str">
+            <v>125-1</v>
+          </cell>
+        </row>
+        <row r="300">
+          <cell r="E300">
+            <v>233.98</v>
+          </cell>
+          <cell r="K300" t="str">
+            <v>125-2</v>
+          </cell>
+        </row>
+        <row r="301">
+          <cell r="E301">
+            <v>233.98</v>
+          </cell>
+          <cell r="K301" t="str">
+            <v>125-3</v>
+          </cell>
+        </row>
+        <row r="302">
+          <cell r="E302">
+            <v>233.98</v>
+          </cell>
+          <cell r="K302" t="str">
+            <v>125-4</v>
+          </cell>
+        </row>
+        <row r="303">
+          <cell r="E303">
+            <v>233.98</v>
+          </cell>
+          <cell r="K303" t="str">
+            <v>125-5</v>
+          </cell>
+        </row>
+        <row r="304">
+          <cell r="E304">
+            <v>229.5</v>
+          </cell>
+          <cell r="K304" t="str">
+            <v>125-6</v>
+          </cell>
+        </row>
+        <row r="305">
+          <cell r="E305">
+            <v>298.69</v>
+          </cell>
+          <cell r="K305" t="str">
+            <v>125-7</v>
+          </cell>
+        </row>
+        <row r="306">
+          <cell r="E306">
+            <v>298.69</v>
+          </cell>
+          <cell r="K306" t="str">
+            <v>125-8</v>
+          </cell>
+        </row>
+        <row r="307">
+          <cell r="E307">
+            <v>298.69</v>
+          </cell>
+          <cell r="K307" t="str">
+            <v>125-9</v>
+          </cell>
+        </row>
+        <row r="308">
+          <cell r="E308">
+            <v>298.69</v>
+          </cell>
+          <cell r="K308" t="str">
+            <v>125-10</v>
+          </cell>
+        </row>
+        <row r="309">
+          <cell r="E309">
+            <v>298.69</v>
+          </cell>
+          <cell r="K309" t="str">
+            <v>125-11</v>
+          </cell>
+        </row>
+        <row r="310">
+          <cell r="E310">
+            <v>298.69</v>
+          </cell>
+          <cell r="K310" t="str">
+            <v>125-12</v>
+          </cell>
+        </row>
+        <row r="311">
+          <cell r="E311">
+            <v>298.69</v>
+          </cell>
+          <cell r="K311" t="str">
+            <v>125-13</v>
+          </cell>
+        </row>
+        <row r="312">
+          <cell r="E312">
+            <v>298.69</v>
+          </cell>
+          <cell r="K312" t="str">
+            <v>125-14</v>
+          </cell>
+        </row>
+        <row r="313">
+          <cell r="E313">
+            <v>229.5</v>
+          </cell>
+          <cell r="K313" t="str">
+            <v>125-15</v>
+          </cell>
+        </row>
+        <row r="314">
+          <cell r="E314">
+            <v>233.98</v>
+          </cell>
+          <cell r="K314" t="str">
+            <v>125-16</v>
+          </cell>
+        </row>
+        <row r="315">
+          <cell r="E315">
+            <v>233.98</v>
+          </cell>
+          <cell r="K315" t="str">
+            <v>125-17</v>
+          </cell>
+        </row>
+        <row r="316">
+          <cell r="E316">
+            <v>233.98</v>
+          </cell>
+          <cell r="K316" t="str">
+            <v>125-18</v>
+          </cell>
+        </row>
+        <row r="317">
+          <cell r="E317">
+            <v>233.98</v>
+          </cell>
+          <cell r="K317" t="str">
+            <v>125-19</v>
+          </cell>
+        </row>
+        <row r="318">
+          <cell r="E318">
+            <v>229.5</v>
+          </cell>
+          <cell r="K318" t="str">
+            <v>125-20</v>
+          </cell>
+        </row>
+        <row r="319">
+          <cell r="E319">
+            <v>298.69</v>
+          </cell>
+          <cell r="K319" t="str">
+            <v>125-21</v>
+          </cell>
+        </row>
+        <row r="320">
+          <cell r="E320">
+            <v>298.69</v>
+          </cell>
+          <cell r="K320" t="str">
+            <v>125-22</v>
+          </cell>
+        </row>
+        <row r="321">
+          <cell r="E321">
+            <v>298.69</v>
+          </cell>
+          <cell r="K321" t="str">
+            <v>125-23</v>
+          </cell>
+        </row>
+        <row r="322">
+          <cell r="E322">
+            <v>298.69</v>
+          </cell>
+          <cell r="K322" t="str">
+            <v>125-24</v>
+          </cell>
+        </row>
+        <row r="323">
+          <cell r="E323">
+            <v>298.69</v>
+          </cell>
+          <cell r="K323" t="str">
+            <v>125-25</v>
+          </cell>
+        </row>
+        <row r="324">
+          <cell r="E324">
+            <v>298.69</v>
+          </cell>
+          <cell r="K324" t="str">
+            <v>125-26</v>
+          </cell>
+        </row>
+        <row r="325">
+          <cell r="E325">
+            <v>298.69</v>
+          </cell>
+          <cell r="K325" t="str">
+            <v>125-27</v>
+          </cell>
+        </row>
+        <row r="326">
+          <cell r="E326">
+            <v>298.69</v>
+          </cell>
+          <cell r="K326" t="str">
+            <v>125-28</v>
+          </cell>
+        </row>
+        <row r="327">
+          <cell r="E327">
+            <v>229.5</v>
+          </cell>
+          <cell r="K327" t="str">
+            <v>126-1</v>
+          </cell>
+        </row>
+        <row r="328">
+          <cell r="E328">
+            <v>233.98</v>
+          </cell>
+          <cell r="K328" t="str">
+            <v>126-2</v>
+          </cell>
+        </row>
+        <row r="329">
+          <cell r="E329">
+            <v>233.98</v>
+          </cell>
+          <cell r="K329" t="str">
+            <v>126-3</v>
+          </cell>
+        </row>
+        <row r="330">
+          <cell r="E330">
+            <v>233.98</v>
+          </cell>
+          <cell r="K330" t="str">
+            <v>126-4</v>
+          </cell>
+        </row>
+        <row r="331">
+          <cell r="E331">
+            <v>233.98</v>
+          </cell>
+          <cell r="K331" t="str">
+            <v>126-5</v>
+          </cell>
+        </row>
+        <row r="332">
+          <cell r="E332">
+            <v>229.5</v>
+          </cell>
+          <cell r="K332" t="str">
+            <v>126-6</v>
+          </cell>
+        </row>
+        <row r="333">
+          <cell r="E333">
+            <v>298.69</v>
+          </cell>
+          <cell r="K333" t="str">
+            <v>126-7</v>
+          </cell>
+        </row>
+        <row r="334">
+          <cell r="E334">
+            <v>298.69</v>
+          </cell>
+          <cell r="K334" t="str">
+            <v>126-8</v>
+          </cell>
+        </row>
+        <row r="335">
+          <cell r="E335">
+            <v>298.69</v>
+          </cell>
+          <cell r="K335" t="str">
+            <v>126-9</v>
+          </cell>
+        </row>
+        <row r="336">
+          <cell r="E336">
+            <v>298.69</v>
+          </cell>
+          <cell r="K336" t="str">
+            <v>126-10</v>
+          </cell>
+        </row>
+        <row r="337">
+          <cell r="E337">
+            <v>298.69</v>
+          </cell>
+          <cell r="K337" t="str">
+            <v>126-11</v>
+          </cell>
+        </row>
+        <row r="338">
+          <cell r="E338">
+            <v>298.69</v>
+          </cell>
+          <cell r="K338" t="str">
+            <v>126-12</v>
+          </cell>
+        </row>
+        <row r="339">
+          <cell r="E339">
+            <v>298.69</v>
+          </cell>
+          <cell r="K339" t="str">
+            <v>126-13</v>
+          </cell>
+        </row>
+        <row r="340">
+          <cell r="E340">
+            <v>298.69</v>
+          </cell>
+          <cell r="K340" t="str">
+            <v>126-14</v>
+          </cell>
+        </row>
+        <row r="341">
+          <cell r="E341">
+            <v>229.5</v>
+          </cell>
+          <cell r="K341" t="str">
+            <v>126-15</v>
+          </cell>
+        </row>
+        <row r="342">
+          <cell r="E342">
+            <v>233.98</v>
+          </cell>
+          <cell r="K342" t="str">
+            <v>126-16</v>
+          </cell>
+        </row>
+        <row r="343">
+          <cell r="E343">
+            <v>233.98</v>
+          </cell>
+          <cell r="K343" t="str">
+            <v>126-17</v>
+          </cell>
+        </row>
+        <row r="344">
+          <cell r="E344">
+            <v>233.98</v>
+          </cell>
+          <cell r="K344" t="str">
+            <v>126-18</v>
+          </cell>
+        </row>
+        <row r="345">
+          <cell r="E345">
+            <v>233.98</v>
+          </cell>
+          <cell r="K345" t="str">
+            <v>126-19</v>
+          </cell>
+        </row>
+        <row r="346">
+          <cell r="E346">
+            <v>229.5</v>
+          </cell>
+          <cell r="K346" t="str">
+            <v>126-20</v>
+          </cell>
+        </row>
+        <row r="347">
+          <cell r="E347">
+            <v>298.69</v>
+          </cell>
+          <cell r="K347" t="str">
+            <v>126-21</v>
+          </cell>
+        </row>
+        <row r="348">
+          <cell r="E348">
+            <v>298.69</v>
+          </cell>
+          <cell r="K348" t="str">
+            <v>126-22</v>
+          </cell>
+        </row>
+        <row r="349">
+          <cell r="E349">
+            <v>298.69</v>
+          </cell>
+          <cell r="K349" t="str">
+            <v>126-23</v>
+          </cell>
+        </row>
+        <row r="350">
+          <cell r="E350">
+            <v>298.69</v>
+          </cell>
+          <cell r="K350" t="str">
+            <v>126-24</v>
+          </cell>
+        </row>
+        <row r="351">
+          <cell r="E351">
+            <v>298.69</v>
+          </cell>
+          <cell r="K351" t="str">
+            <v>126-25</v>
+          </cell>
+        </row>
+        <row r="352">
+          <cell r="E352">
+            <v>298.69</v>
+          </cell>
+          <cell r="K352" t="str">
+            <v>126-26</v>
+          </cell>
+        </row>
+        <row r="353">
+          <cell r="E353">
+            <v>298.69</v>
+          </cell>
+          <cell r="K353" t="str">
+            <v>126-27</v>
+          </cell>
+        </row>
+        <row r="354">
+          <cell r="E354">
+            <v>298.69</v>
+          </cell>
+          <cell r="K354" t="str">
+            <v>126-28</v>
+          </cell>
+        </row>
+        <row r="355">
+          <cell r="E355">
+            <v>0</v>
+          </cell>
+          <cell r="K355" t="str">
+            <v>156-</v>
+          </cell>
+        </row>
+        <row r="356">
+          <cell r="E356">
+            <v>283</v>
+          </cell>
+          <cell r="K356" t="str">
+            <v>156-2A</v>
+          </cell>
+        </row>
+        <row r="357">
+          <cell r="E357">
+            <v>280.5</v>
+          </cell>
+          <cell r="K357" t="str">
+            <v>156-3A</v>
+          </cell>
+        </row>
+        <row r="358">
+          <cell r="E358">
+            <v>278</v>
+          </cell>
+          <cell r="K358" t="str">
+            <v>156-4A</v>
+          </cell>
+        </row>
+        <row r="359">
+          <cell r="E359">
+            <v>275</v>
+          </cell>
+          <cell r="K359" t="str">
+            <v>156-5A</v>
+          </cell>
+        </row>
+        <row r="360">
+          <cell r="E360">
+            <v>266</v>
+          </cell>
+          <cell r="K360" t="str">
+            <v>156-6A</v>
+          </cell>
+        </row>
+        <row r="361">
+          <cell r="E361">
+            <v>298.69</v>
+          </cell>
+          <cell r="K361" t="str">
+            <v>156-8</v>
+          </cell>
+        </row>
+        <row r="362">
+          <cell r="E362">
+            <v>298.69</v>
+          </cell>
+          <cell r="K362" t="str">
+            <v>156-9</v>
+          </cell>
+        </row>
+        <row r="363">
+          <cell r="E363">
+            <v>298.69</v>
+          </cell>
+          <cell r="K363" t="str">
+            <v>156-10</v>
+          </cell>
+        </row>
+        <row r="364">
+          <cell r="E364">
+            <v>298.69</v>
+          </cell>
+          <cell r="K364" t="str">
+            <v>156-11</v>
+          </cell>
+        </row>
+        <row r="365">
+          <cell r="E365">
+            <v>298.69</v>
+          </cell>
+          <cell r="K365" t="str">
+            <v>156-12</v>
+          </cell>
+        </row>
+        <row r="366">
+          <cell r="E366">
+            <v>298.69</v>
+          </cell>
+          <cell r="K366" t="str">
+            <v>156-13</v>
+          </cell>
+        </row>
+        <row r="367">
+          <cell r="E367">
+            <v>298.69</v>
+          </cell>
+          <cell r="K367" t="str">
+            <v>156-14</v>
+          </cell>
+        </row>
+        <row r="368">
+          <cell r="E368">
+            <v>298.69</v>
+          </cell>
+          <cell r="K368" t="str">
+            <v>156-15</v>
+          </cell>
+        </row>
+        <row r="369">
+          <cell r="E369">
+            <v>298.69</v>
+          </cell>
+          <cell r="K369" t="str">
+            <v>156-16</v>
+          </cell>
+        </row>
+        <row r="370">
+          <cell r="E370">
+            <v>298.69</v>
+          </cell>
+          <cell r="K370" t="str">
+            <v>156-17</v>
+          </cell>
+        </row>
+        <row r="371">
+          <cell r="E371">
+            <v>226.59</v>
+          </cell>
+          <cell r="K371" t="str">
+            <v>156-18</v>
+          </cell>
+        </row>
+        <row r="372">
+          <cell r="E372">
+            <v>230.83</v>
+          </cell>
+          <cell r="K372" t="str">
+            <v>156-19</v>
+          </cell>
+        </row>
+        <row r="373">
+          <cell r="E373">
+            <v>230.88</v>
+          </cell>
+          <cell r="K373" t="str">
+            <v>156-20</v>
+          </cell>
+        </row>
+        <row r="374">
+          <cell r="E374">
+            <v>230.88</v>
+          </cell>
+          <cell r="K374" t="str">
+            <v>156-21</v>
+          </cell>
+        </row>
+        <row r="375">
+          <cell r="E375">
+            <v>230.93</v>
+          </cell>
+          <cell r="K375" t="str">
+            <v>156-22</v>
+          </cell>
+        </row>
+        <row r="376">
+          <cell r="E376">
+            <v>226.48</v>
+          </cell>
+          <cell r="K376" t="str">
+            <v>156-23</v>
+          </cell>
+        </row>
+        <row r="377">
+          <cell r="E377">
+            <v>0</v>
+          </cell>
+          <cell r="K377" t="str">
+            <v>156-</v>
+          </cell>
+        </row>
+        <row r="378">
+          <cell r="E378">
+            <v>298.69</v>
+          </cell>
+          <cell r="K378" t="str">
+            <v>156-25</v>
+          </cell>
+        </row>
+        <row r="379">
+          <cell r="E379">
+            <v>298.69</v>
+          </cell>
+          <cell r="K379" t="str">
+            <v>156-26</v>
+          </cell>
+        </row>
+        <row r="380">
+          <cell r="E380">
+            <v>298.69</v>
+          </cell>
+          <cell r="K380" t="str">
+            <v>156-27</v>
+          </cell>
+        </row>
+        <row r="381">
+          <cell r="E381">
+            <v>298.69</v>
+          </cell>
+          <cell r="K381" t="str">
+            <v>156-28</v>
+          </cell>
+        </row>
+        <row r="382">
+          <cell r="E382">
+            <v>298.69</v>
+          </cell>
+          <cell r="K382" t="str">
+            <v>156-29</v>
+          </cell>
+        </row>
+        <row r="383">
+          <cell r="E383">
+            <v>0</v>
+          </cell>
+          <cell r="K383" t="str">
+            <v>156-</v>
+          </cell>
+        </row>
+        <row r="384">
+          <cell r="E384">
+            <v>0</v>
+          </cell>
+          <cell r="K384" t="str">
+            <v>156-</v>
+          </cell>
+        </row>
+        <row r="385">
+          <cell r="E385">
+            <v>298.69</v>
+          </cell>
+          <cell r="K385" t="str">
+            <v>156-32</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -1414,8 +4482,13 @@
       <c r="L2" s="12">
         <v>2340837</v>
       </c>
-      <c r="M2" s="13"/>
-      <c r="N2" s="14"/>
+      <c r="M2" s="13">
+        <f>+_xlfn.XLOOKUP(D2&amp;"-"&amp;E2,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>230.52</v>
+      </c>
+      <c r="N2" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O2" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -1481,8 +4554,13 @@
       <c r="L3" s="12">
         <v>2371238</v>
       </c>
-      <c r="M3" s="13"/>
-      <c r="N3" s="14"/>
+      <c r="M3" s="13">
+        <f>+_xlfn.XLOOKUP(D3&amp;"-"&amp;E3,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N3" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O3" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -1548,8 +4626,13 @@
       <c r="L4" s="12">
         <v>1865606</v>
       </c>
-      <c r="M4" s="13"/>
-      <c r="N4" s="14"/>
+      <c r="M4" s="13">
+        <f>+_xlfn.XLOOKUP(D4&amp;"-"&amp;E4,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N4" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O4" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -1615,8 +4698,13 @@
       <c r="L5" s="12">
         <v>1865606</v>
       </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="14"/>
+      <c r="M5" s="13">
+        <f>+_xlfn.XLOOKUP(D5&amp;"-"&amp;E5,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N5" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O5" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -1682,8 +4770,13 @@
       <c r="L6" s="12">
         <v>1865606</v>
       </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="14"/>
+      <c r="M6" s="13">
+        <f>+_xlfn.XLOOKUP(D6&amp;"-"&amp;E6,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N6" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O6" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -1749,8 +4842,13 @@
       <c r="L7" s="12">
         <v>1865606</v>
       </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="14"/>
+      <c r="M7" s="13">
+        <f>+_xlfn.XLOOKUP(D7&amp;"-"&amp;E7,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N7" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O7" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -1816,8 +4914,13 @@
       <c r="L8" s="12">
         <v>2440026</v>
       </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="14"/>
+      <c r="M8" s="13">
+        <f>+_xlfn.XLOOKUP(D8&amp;"-"&amp;E8,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N8" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O8" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -1883,8 +4986,13 @@
       <c r="L9" s="12">
         <v>2668984</v>
       </c>
-      <c r="M9" s="13"/>
-      <c r="N9" s="14"/>
+      <c r="M9" s="13">
+        <f>+_xlfn.XLOOKUP(D9&amp;"-"&amp;E9,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N9" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O9" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -1950,8 +5058,13 @@
       <c r="L10" s="12">
         <v>2668984</v>
       </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="14"/>
+      <c r="M10" s="13">
+        <f>+_xlfn.XLOOKUP(D10&amp;"-"&amp;E10,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N10" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O10" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -2017,8 +5130,13 @@
       <c r="L11" s="12">
         <v>2668984</v>
       </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="14"/>
+      <c r="M11" s="13">
+        <f>+_xlfn.XLOOKUP(D11&amp;"-"&amp;E11,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N11" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O11" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -2084,8 +5202,13 @@
       <c r="L12" s="12">
         <v>2668984</v>
       </c>
-      <c r="M12" s="13"/>
-      <c r="N12" s="14"/>
+      <c r="M12" s="13">
+        <f>+_xlfn.XLOOKUP(D12&amp;"-"&amp;E12,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N12" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O12" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -2151,8 +5274,13 @@
       <c r="L13" s="12">
         <v>2668984</v>
       </c>
-      <c r="M13" s="13"/>
-      <c r="N13" s="14"/>
+      <c r="M13" s="13">
+        <f>+_xlfn.XLOOKUP(D13&amp;"-"&amp;E13,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N13" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O13" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -2218,8 +5346,13 @@
       <c r="L14" s="12">
         <v>2668984</v>
       </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="14"/>
+      <c r="M14" s="13">
+        <f>+_xlfn.XLOOKUP(D14&amp;"-"&amp;E14,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N14" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O14" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -2285,8 +5418,13 @@
       <c r="L15" s="12">
         <v>2668984</v>
       </c>
-      <c r="M15" s="13"/>
-      <c r="N15" s="14"/>
+      <c r="M15" s="13">
+        <f>+_xlfn.XLOOKUP(D15&amp;"-"&amp;E15,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N15" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O15" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -2352,8 +5490,13 @@
       <c r="L16" s="12">
         <v>2668984</v>
       </c>
-      <c r="M16" s="13"/>
-      <c r="N16" s="14"/>
+      <c r="M16" s="13">
+        <f>+_xlfn.XLOOKUP(D16&amp;"-"&amp;E16,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N16" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O16" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -2419,8 +5562,13 @@
       <c r="L17" s="12">
         <v>2440026</v>
       </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="14"/>
+      <c r="M17" s="13">
+        <f>+_xlfn.XLOOKUP(D17&amp;"-"&amp;E17,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N17" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O17" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -2486,8 +5634,13 @@
       <c r="L18" s="12">
         <v>1865606</v>
       </c>
-      <c r="M18" s="13"/>
-      <c r="N18" s="14"/>
+      <c r="M18" s="13">
+        <f>+_xlfn.XLOOKUP(D18&amp;"-"&amp;E18,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N18" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O18" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -2553,8 +5706,13 @@
       <c r="L19" s="12">
         <v>1865606</v>
       </c>
-      <c r="M19" s="13"/>
-      <c r="N19" s="14"/>
+      <c r="M19" s="13">
+        <f>+_xlfn.XLOOKUP(D19&amp;"-"&amp;E19,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N19" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O19" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -2620,8 +5778,13 @@
       <c r="L20" s="12">
         <v>1865606</v>
       </c>
-      <c r="M20" s="13"/>
-      <c r="N20" s="14"/>
+      <c r="M20" s="13">
+        <f>+_xlfn.XLOOKUP(D20&amp;"-"&amp;E20,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N20" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O20" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -2687,8 +5850,13 @@
       <c r="L21" s="12">
         <v>1865606</v>
       </c>
-      <c r="M21" s="13"/>
-      <c r="N21" s="14"/>
+      <c r="M21" s="13">
+        <f>+_xlfn.XLOOKUP(D21&amp;"-"&amp;E21,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N21" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O21" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -2754,8 +5922,13 @@
       <c r="L22" s="12">
         <v>1865606</v>
       </c>
-      <c r="M22" s="13"/>
-      <c r="N22" s="14"/>
+      <c r="M22" s="13">
+        <f>+_xlfn.XLOOKUP(D22&amp;"-"&amp;E22,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N22" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O22" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -2821,8 +5994,13 @@
       <c r="L23" s="12">
         <v>2340837</v>
       </c>
-      <c r="M23" s="13"/>
-      <c r="N23" s="14"/>
+      <c r="M23" s="13">
+        <f>+_xlfn.XLOOKUP(D23&amp;"-"&amp;E23,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>230.52</v>
+      </c>
+      <c r="N23" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O23" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -2888,8 +6066,13 @@
       <c r="L24" s="12">
         <v>2013674</v>
       </c>
-      <c r="M24" s="13"/>
-      <c r="N24" s="14"/>
+      <c r="M24" s="13">
+        <f>+_xlfn.XLOOKUP(D24&amp;"-"&amp;E24,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>235</v>
+      </c>
+      <c r="N24" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O24" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -2955,8 +6138,13 @@
       <c r="L25" s="12">
         <v>2675690</v>
       </c>
-      <c r="M25" s="13"/>
-      <c r="N25" s="14"/>
+      <c r="M25" s="13">
+        <f>+_xlfn.XLOOKUP(D25&amp;"-"&amp;E25,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N25" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O25" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -3022,8 +6210,13 @@
       <c r="L26" s="12">
         <v>2675690</v>
       </c>
-      <c r="M26" s="13"/>
-      <c r="N26" s="14"/>
+      <c r="M26" s="13">
+        <f>+_xlfn.XLOOKUP(D26&amp;"-"&amp;E26,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N26" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O26" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -3089,8 +6282,13 @@
       <c r="L27" s="12">
         <v>2675690</v>
       </c>
-      <c r="M27" s="13"/>
-      <c r="N27" s="14"/>
+      <c r="M27" s="13">
+        <f>+_xlfn.XLOOKUP(D27&amp;"-"&amp;E27,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N27" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O27" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -3156,8 +6354,13 @@
       <c r="L28" s="12">
         <v>2675690</v>
       </c>
-      <c r="M28" s="13"/>
-      <c r="N28" s="14"/>
+      <c r="M28" s="13">
+        <f>+_xlfn.XLOOKUP(D28&amp;"-"&amp;E28,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N28" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O28" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -3223,8 +6426,13 @@
       <c r="L29" s="12">
         <v>2675690</v>
       </c>
-      <c r="M29" s="13"/>
-      <c r="N29" s="14"/>
+      <c r="M29" s="13">
+        <f>+_xlfn.XLOOKUP(D29&amp;"-"&amp;E29,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N29" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O29" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -3290,8 +6498,13 @@
       <c r="L30" s="12">
         <v>2675690</v>
       </c>
-      <c r="M30" s="13"/>
-      <c r="N30" s="14"/>
+      <c r="M30" s="13">
+        <f>+_xlfn.XLOOKUP(D30&amp;"-"&amp;E30,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N30" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O30" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -3357,8 +6570,13 @@
       <c r="L31" s="12">
         <v>2675690</v>
       </c>
-      <c r="M31" s="13"/>
-      <c r="N31" s="14"/>
+      <c r="M31" s="13">
+        <f>+_xlfn.XLOOKUP(D31&amp;"-"&amp;E31,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N31" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O31" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -3424,8 +6642,13 @@
       <c r="L32" s="12">
         <v>2675690</v>
       </c>
-      <c r="M32" s="13"/>
-      <c r="N32" s="14"/>
+      <c r="M32" s="13">
+        <f>+_xlfn.XLOOKUP(D32&amp;"-"&amp;E32,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N32" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O32" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -3491,8 +6714,13 @@
       <c r="L33" s="12">
         <v>2013674</v>
       </c>
-      <c r="M33" s="13"/>
-      <c r="N33" s="14"/>
+      <c r="M33" s="13">
+        <f>+_xlfn.XLOOKUP(D33&amp;"-"&amp;E33,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>235</v>
+      </c>
+      <c r="N33" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O33" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -3558,8 +6786,13 @@
       <c r="L34" s="12">
         <v>2320570</v>
       </c>
-      <c r="M34" s="13"/>
-      <c r="N34" s="14"/>
+      <c r="M34" s="13">
+        <f>+_xlfn.XLOOKUP(D34&amp;"-"&amp;E34,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N34" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O34" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -3625,8 +6858,13 @@
       <c r="L35" s="12">
         <v>1865606</v>
       </c>
-      <c r="M35" s="13"/>
-      <c r="N35" s="14"/>
+      <c r="M35" s="13">
+        <f>+_xlfn.XLOOKUP(D35&amp;"-"&amp;E35,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N35" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O35" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -3692,8 +6930,13 @@
       <c r="L36" s="12">
         <v>1865606</v>
       </c>
-      <c r="M36" s="13"/>
-      <c r="N36" s="14"/>
+      <c r="M36" s="13">
+        <f>+_xlfn.XLOOKUP(D36&amp;"-"&amp;E36,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N36" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O36" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -3759,8 +7002,13 @@
       <c r="L37" s="12">
         <v>1865606</v>
       </c>
-      <c r="M37" s="13"/>
-      <c r="N37" s="14"/>
+      <c r="M37" s="13">
+        <f>+_xlfn.XLOOKUP(D37&amp;"-"&amp;E37,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N37" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O37" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -3826,8 +7074,13 @@
       <c r="L38" s="12">
         <v>1865606</v>
       </c>
-      <c r="M38" s="13"/>
-      <c r="N38" s="14"/>
+      <c r="M38" s="13">
+        <f>+_xlfn.XLOOKUP(D38&amp;"-"&amp;E38,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N38" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O38" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -3893,8 +7146,13 @@
       <c r="L39" s="12">
         <v>2320570</v>
       </c>
-      <c r="M39" s="13"/>
-      <c r="N39" s="14"/>
+      <c r="M39" s="13">
+        <f>+_xlfn.XLOOKUP(D39&amp;"-"&amp;E39,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N39" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O39" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -3960,8 +7218,13 @@
       <c r="L40" s="12">
         <v>2227878</v>
       </c>
-      <c r="M40" s="13"/>
-      <c r="N40" s="14"/>
+      <c r="M40" s="13">
+        <f>+_xlfn.XLOOKUP(D40&amp;"-"&amp;E40,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N40" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O40" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -4027,8 +7290,13 @@
       <c r="L41" s="12">
         <v>2227878</v>
       </c>
-      <c r="M41" s="13"/>
-      <c r="N41" s="14"/>
+      <c r="M41" s="13">
+        <f>+_xlfn.XLOOKUP(D41&amp;"-"&amp;E41,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N41" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O41" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -4094,8 +7362,13 @@
       <c r="L42" s="12">
         <v>2227878</v>
       </c>
-      <c r="M42" s="13"/>
-      <c r="N42" s="14"/>
+      <c r="M42" s="13">
+        <f>+_xlfn.XLOOKUP(D42&amp;"-"&amp;E42,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N42" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O42" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -4161,8 +7434,13 @@
       <c r="L43" s="12">
         <v>2227878</v>
       </c>
-      <c r="M43" s="13"/>
-      <c r="N43" s="14"/>
+      <c r="M43" s="13">
+        <f>+_xlfn.XLOOKUP(D43&amp;"-"&amp;E43,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N43" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O43" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -4228,8 +7506,13 @@
       <c r="L44" s="12">
         <v>2227878</v>
       </c>
-      <c r="M44" s="13"/>
-      <c r="N44" s="14"/>
+      <c r="M44" s="13">
+        <f>+_xlfn.XLOOKUP(D44&amp;"-"&amp;E44,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N44" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O44" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -4295,8 +7578,13 @@
       <c r="L45" s="12">
         <v>2227878</v>
       </c>
-      <c r="M45" s="13"/>
-      <c r="N45" s="14"/>
+      <c r="M45" s="13">
+        <f>+_xlfn.XLOOKUP(D45&amp;"-"&amp;E45,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N45" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O45" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -4362,8 +7650,13 @@
       <c r="L46" s="12">
         <v>2227878</v>
       </c>
-      <c r="M46" s="13"/>
-      <c r="N46" s="14"/>
+      <c r="M46" s="13">
+        <f>+_xlfn.XLOOKUP(D46&amp;"-"&amp;E46,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N46" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O46" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -4429,8 +7722,13 @@
       <c r="L47" s="12">
         <v>2227878</v>
       </c>
-      <c r="M47" s="13"/>
-      <c r="N47" s="14"/>
+      <c r="M47" s="13">
+        <f>+_xlfn.XLOOKUP(D47&amp;"-"&amp;E47,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N47" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O47" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -4496,8 +7794,13 @@
       <c r="L48" s="12">
         <v>2320570</v>
       </c>
-      <c r="M48" s="13"/>
-      <c r="N48" s="14"/>
+      <c r="M48" s="13">
+        <f>+_xlfn.XLOOKUP(D48&amp;"-"&amp;E48,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N48" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O48" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -4563,8 +7866,13 @@
       <c r="L49" s="12">
         <v>1865606</v>
       </c>
-      <c r="M49" s="13"/>
-      <c r="N49" s="14"/>
+      <c r="M49" s="13">
+        <f>+_xlfn.XLOOKUP(D49&amp;"-"&amp;E49,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N49" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O49" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -4630,8 +7938,13 @@
       <c r="L50" s="12">
         <v>1865606</v>
       </c>
-      <c r="M50" s="13"/>
-      <c r="N50" s="14"/>
+      <c r="M50" s="13">
+        <f>+_xlfn.XLOOKUP(D50&amp;"-"&amp;E50,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N50" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O50" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -4697,8 +8010,13 @@
       <c r="L51" s="12">
         <v>1865606</v>
       </c>
-      <c r="M51" s="13"/>
-      <c r="N51" s="14"/>
+      <c r="M51" s="13">
+        <f>+_xlfn.XLOOKUP(D51&amp;"-"&amp;E51,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N51" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O51" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -4764,8 +8082,13 @@
       <c r="L52" s="12">
         <v>1865606</v>
       </c>
-      <c r="M52" s="13"/>
-      <c r="N52" s="14"/>
+      <c r="M52" s="13">
+        <f>+_xlfn.XLOOKUP(D52&amp;"-"&amp;E52,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N52" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O52" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -4831,8 +8154,13 @@
       <c r="L53" s="12">
         <v>2320570</v>
       </c>
-      <c r="M53" s="13"/>
-      <c r="N53" s="14"/>
+      <c r="M53" s="13">
+        <f>+_xlfn.XLOOKUP(D53&amp;"-"&amp;E53,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N53" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O53" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -4898,8 +8226,13 @@
       <c r="L54" s="12">
         <v>2227878</v>
       </c>
-      <c r="M54" s="13"/>
-      <c r="N54" s="14"/>
+      <c r="M54" s="13">
+        <f>+_xlfn.XLOOKUP(D54&amp;"-"&amp;E54,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N54" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O54" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -4965,8 +8298,13 @@
       <c r="L55" s="12">
         <v>4010182</v>
       </c>
-      <c r="M55" s="13"/>
-      <c r="N55" s="14"/>
+      <c r="M55" s="13">
+        <f>+_xlfn.XLOOKUP(D55&amp;"-"&amp;E55,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N55" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O55" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -5032,8 +8370,13 @@
       <c r="L56" s="12">
         <v>2227878</v>
       </c>
-      <c r="M56" s="13"/>
-      <c r="N56" s="14"/>
+      <c r="M56" s="13">
+        <f>+_xlfn.XLOOKUP(D56&amp;"-"&amp;E56,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N56" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O56" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -5099,8 +8442,13 @@
       <c r="L57" s="12">
         <v>2227878</v>
       </c>
-      <c r="M57" s="13"/>
-      <c r="N57" s="14"/>
+      <c r="M57" s="13">
+        <f>+_xlfn.XLOOKUP(D57&amp;"-"&amp;E57,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N57" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O57" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -5166,8 +8514,13 @@
       <c r="L58" s="12">
         <v>2227878</v>
       </c>
-      <c r="M58" s="13"/>
-      <c r="N58" s="14"/>
+      <c r="M58" s="13">
+        <f>+_xlfn.XLOOKUP(D58&amp;"-"&amp;E58,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N58" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O58" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -5233,8 +8586,13 @@
       <c r="L59" s="12">
         <v>2227878</v>
       </c>
-      <c r="M59" s="13"/>
-      <c r="N59" s="14"/>
+      <c r="M59" s="13">
+        <f>+_xlfn.XLOOKUP(D59&amp;"-"&amp;E59,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N59" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O59" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -5300,8 +8658,13 @@
       <c r="L60" s="12">
         <v>2227878</v>
       </c>
-      <c r="M60" s="13"/>
-      <c r="N60" s="14"/>
+      <c r="M60" s="13">
+        <f>+_xlfn.XLOOKUP(D60&amp;"-"&amp;E60,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N60" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O60" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -5367,8 +8730,13 @@
       <c r="L61" s="12">
         <v>2227878</v>
       </c>
-      <c r="M61" s="13"/>
-      <c r="N61" s="14"/>
+      <c r="M61" s="13">
+        <f>+_xlfn.XLOOKUP(D61&amp;"-"&amp;E61,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N61" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O61" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -5435,7 +8803,8 @@
         <v>2440026</v>
       </c>
       <c r="M62" s="13">
-        <v>229</v>
+        <f>+_xlfn.XLOOKUP(D62&amp;"-"&amp;E62,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
       </c>
       <c r="N62" s="20" t="s">
         <v>24</v>
@@ -5510,7 +8879,8 @@
         <v>1865606</v>
       </c>
       <c r="M63" s="13">
-        <v>234</v>
+        <f>+_xlfn.XLOOKUP(D63&amp;"-"&amp;E63,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
       </c>
       <c r="N63" s="20" t="s">
         <v>24</v>
@@ -5585,7 +8955,8 @@
         <v>1865606</v>
       </c>
       <c r="M64" s="13">
-        <v>234</v>
+        <f>+_xlfn.XLOOKUP(D64&amp;"-"&amp;E64,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
       </c>
       <c r="N64" s="20" t="s">
         <v>24</v>
@@ -5660,7 +9031,8 @@
         <v>1865606</v>
       </c>
       <c r="M65" s="13">
-        <v>234</v>
+        <f>+_xlfn.XLOOKUP(D65&amp;"-"&amp;E65,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
       </c>
       <c r="N65" s="20" t="s">
         <v>24</v>
@@ -5735,7 +9107,8 @@
         <v>2440026</v>
       </c>
       <c r="M66" s="13">
-        <v>229</v>
+        <f>+_xlfn.XLOOKUP(D66&amp;"-"&amp;E66,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
       </c>
       <c r="N66" s="20" t="s">
         <v>24</v>
@@ -5810,7 +9183,8 @@
         <v>2227878</v>
       </c>
       <c r="M67" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D67&amp;"-"&amp;E67,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N67" s="20" t="s">
         <v>24</v>
@@ -5885,7 +9259,8 @@
         <v>2227878</v>
       </c>
       <c r="M68" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D68&amp;"-"&amp;E68,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N68" s="20" t="s">
         <v>24</v>
@@ -5960,7 +9335,8 @@
         <v>2227878</v>
       </c>
       <c r="M69" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D69&amp;"-"&amp;E69,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N69" s="20" t="s">
         <v>24</v>
@@ -6035,7 +9411,8 @@
         <v>2227878</v>
       </c>
       <c r="M70" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D70&amp;"-"&amp;E70,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N70" s="20" t="s">
         <v>24</v>
@@ -6110,7 +9487,8 @@
         <v>2227878</v>
       </c>
       <c r="M71" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D71&amp;"-"&amp;E71,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N71" s="20" t="s">
         <v>24</v>
@@ -6185,7 +9563,8 @@
         <v>2227878</v>
       </c>
       <c r="M72" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D72&amp;"-"&amp;E72,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N72" s="20" t="s">
         <v>24</v>
@@ -6260,7 +9639,8 @@
         <v>2227878</v>
       </c>
       <c r="M73" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D73&amp;"-"&amp;E73,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N73" s="20" t="s">
         <v>24</v>
@@ -6335,7 +9715,8 @@
         <v>2440026</v>
       </c>
       <c r="M74" s="13">
-        <v>229</v>
+        <f>+_xlfn.XLOOKUP(D74&amp;"-"&amp;E74,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
       </c>
       <c r="N74" s="20" t="s">
         <v>24</v>
@@ -6410,7 +9791,8 @@
         <v>1865606</v>
       </c>
       <c r="M75" s="13">
-        <v>234</v>
+        <f>+_xlfn.XLOOKUP(D75&amp;"-"&amp;E75,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
       </c>
       <c r="N75" s="20" t="s">
         <v>24</v>
@@ -6485,7 +9867,8 @@
         <v>1865606</v>
       </c>
       <c r="M76" s="13">
-        <v>234</v>
+        <f>+_xlfn.XLOOKUP(D76&amp;"-"&amp;E76,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
       </c>
       <c r="N76" s="20" t="s">
         <v>24</v>
@@ -6560,7 +9943,8 @@
         <v>1865606</v>
       </c>
       <c r="M77" s="13">
-        <v>234</v>
+        <f>+_xlfn.XLOOKUP(D77&amp;"-"&amp;E77,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
       </c>
       <c r="N77" s="20" t="s">
         <v>24</v>
@@ -6635,7 +10019,8 @@
         <v>1865606</v>
       </c>
       <c r="M78" s="13">
-        <v>234</v>
+        <f>+_xlfn.XLOOKUP(D78&amp;"-"&amp;E78,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
       </c>
       <c r="N78" s="20" t="s">
         <v>24</v>
@@ -6710,7 +10095,8 @@
         <v>2440026</v>
       </c>
       <c r="M79" s="13">
-        <v>229</v>
+        <f>+_xlfn.XLOOKUP(D79&amp;"-"&amp;E79,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
       </c>
       <c r="N79" s="20" t="s">
         <v>24</v>
@@ -6785,7 +10171,8 @@
         <v>2227878</v>
       </c>
       <c r="M80" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D80&amp;"-"&amp;E80,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N80" s="20" t="s">
         <v>24</v>
@@ -6860,7 +10247,8 @@
         <v>2227878</v>
       </c>
       <c r="M81" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D81&amp;"-"&amp;E81,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N81" s="20" t="s">
         <v>24</v>
@@ -6935,7 +10323,8 @@
         <v>2227878</v>
       </c>
       <c r="M82" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D82&amp;"-"&amp;E82,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N82" s="20" t="s">
         <v>24</v>
@@ -7010,7 +10399,8 @@
         <v>2227878</v>
       </c>
       <c r="M83" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D83&amp;"-"&amp;E83,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N83" s="20" t="s">
         <v>24</v>
@@ -7085,7 +10475,8 @@
         <v>2227878</v>
       </c>
       <c r="M84" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D84&amp;"-"&amp;E84,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N84" s="20" t="s">
         <v>24</v>
@@ -7160,7 +10551,8 @@
         <v>2227878</v>
       </c>
       <c r="M85" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D85&amp;"-"&amp;E85,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N85" s="20" t="s">
         <v>24</v>
@@ -7235,7 +10627,8 @@
         <v>2227878</v>
       </c>
       <c r="M86" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D86&amp;"-"&amp;E86,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N86" s="20" t="s">
         <v>24</v>
@@ -7310,7 +10703,8 @@
         <v>2227878</v>
       </c>
       <c r="M87" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D87&amp;"-"&amp;E87,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N87" s="20" t="s">
         <v>24</v>
@@ -7384,10 +10778,13 @@
       <c r="L88" s="12">
         <v>2461336</v>
       </c>
-      <c r="M88" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N88" s="14"/>
+      <c r="M88" s="13">
+        <f>+_xlfn.XLOOKUP(D88&amp;"-"&amp;E88,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>230.52</v>
+      </c>
+      <c r="N88" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O88" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -7453,10 +10850,13 @@
       <c r="L89" s="12">
         <v>1865606</v>
       </c>
-      <c r="M89" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N89" s="14"/>
+      <c r="M89" s="13">
+        <f>+_xlfn.XLOOKUP(D89&amp;"-"&amp;E89,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N89" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O89" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -7522,10 +10922,13 @@
       <c r="L90" s="12">
         <v>1865606</v>
       </c>
-      <c r="M90" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N90" s="14"/>
+      <c r="M90" s="13">
+        <f>+_xlfn.XLOOKUP(D90&amp;"-"&amp;E90,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N90" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O90" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -7591,10 +10994,13 @@
       <c r="L91" s="12">
         <v>1865606</v>
       </c>
-      <c r="M91" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N91" s="14"/>
+      <c r="M91" s="13">
+        <f>+_xlfn.XLOOKUP(D91&amp;"-"&amp;E91,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N91" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O91" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -7660,10 +11066,13 @@
       <c r="L92" s="12">
         <v>1865606</v>
       </c>
-      <c r="M92" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N92" s="14"/>
+      <c r="M92" s="13">
+        <f>+_xlfn.XLOOKUP(D92&amp;"-"&amp;E92,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N92" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O92" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -7729,10 +11138,13 @@
       <c r="L93" s="12">
         <v>1865606</v>
       </c>
-      <c r="M93" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N93" s="14"/>
+      <c r="M93" s="13">
+        <f>+_xlfn.XLOOKUP(D93&amp;"-"&amp;E93,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N93" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O93" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -7798,10 +11210,13 @@
       <c r="L94" s="12">
         <v>2668984</v>
       </c>
-      <c r="M94" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N94" s="14"/>
+      <c r="M94" s="13">
+        <f>+_xlfn.XLOOKUP(D94&amp;"-"&amp;E94,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N94" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O94" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -7867,10 +11282,13 @@
       <c r="L95" s="12">
         <v>2668984</v>
       </c>
-      <c r="M95" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N95" s="14"/>
+      <c r="M95" s="13">
+        <f>+_xlfn.XLOOKUP(D95&amp;"-"&amp;E95,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N95" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O95" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -7936,10 +11354,13 @@
       <c r="L96" s="12">
         <v>2668984</v>
       </c>
-      <c r="M96" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N96" s="14"/>
+      <c r="M96" s="13">
+        <f>+_xlfn.XLOOKUP(D96&amp;"-"&amp;E96,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N96" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O96" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -8005,10 +11426,13 @@
       <c r="L97" s="12">
         <v>2668984</v>
       </c>
-      <c r="M97" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N97" s="14"/>
+      <c r="M97" s="13">
+        <f>+_xlfn.XLOOKUP(D97&amp;"-"&amp;E97,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N97" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O97" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -8074,10 +11498,13 @@
       <c r="L98" s="12">
         <v>2668984</v>
       </c>
-      <c r="M98" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N98" s="14"/>
+      <c r="M98" s="13">
+        <f>+_xlfn.XLOOKUP(D98&amp;"-"&amp;E98,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N98" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O98" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -8143,10 +11570,13 @@
       <c r="L99" s="12">
         <v>2668984</v>
       </c>
-      <c r="M99" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N99" s="14"/>
+      <c r="M99" s="13">
+        <f>+_xlfn.XLOOKUP(D99&amp;"-"&amp;E99,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N99" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O99" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -8212,10 +11642,13 @@
       <c r="L100" s="12">
         <v>2440026</v>
       </c>
-      <c r="M100" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N100" s="14"/>
+      <c r="M100" s="13">
+        <f>+_xlfn.XLOOKUP(D100&amp;"-"&amp;E100,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N100" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O100" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -8281,10 +11714,13 @@
       <c r="L101" s="12">
         <v>1865606</v>
       </c>
-      <c r="M101" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N101" s="14"/>
+      <c r="M101" s="13">
+        <f>+_xlfn.XLOOKUP(D101&amp;"-"&amp;E101,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N101" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O101" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -8350,10 +11786,13 @@
       <c r="L102" s="12">
         <v>1865606</v>
       </c>
-      <c r="M102" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N102" s="14"/>
+      <c r="M102" s="13">
+        <f>+_xlfn.XLOOKUP(D102&amp;"-"&amp;E102,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N102" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O102" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -8419,10 +11858,13 @@
       <c r="L103" s="12">
         <v>1865606</v>
       </c>
-      <c r="M103" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N103" s="14"/>
+      <c r="M103" s="13">
+        <f>+_xlfn.XLOOKUP(D103&amp;"-"&amp;E103,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N103" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O103" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -8488,10 +11930,13 @@
       <c r="L104" s="12">
         <v>1865606</v>
       </c>
-      <c r="M104" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N104" s="14"/>
+      <c r="M104" s="13">
+        <f>+_xlfn.XLOOKUP(D104&amp;"-"&amp;E104,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N104" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O104" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -8557,10 +12002,13 @@
       <c r="L105" s="12">
         <v>1865606</v>
       </c>
-      <c r="M105" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N105" s="14"/>
+      <c r="M105" s="13">
+        <f>+_xlfn.XLOOKUP(D105&amp;"-"&amp;E105,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N105" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O105" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -8626,10 +12074,13 @@
       <c r="L106" s="12">
         <v>2269545</v>
       </c>
-      <c r="M106" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N106" s="14"/>
+      <c r="M106" s="13">
+        <f>+_xlfn.XLOOKUP(D106&amp;"-"&amp;E106,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>212.94</v>
+      </c>
+      <c r="N106" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O106" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -8695,10 +12146,13 @@
       <c r="L107" s="12">
         <v>1873593</v>
       </c>
-      <c r="M107" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N107" s="14"/>
+      <c r="M107" s="13">
+        <f>+_xlfn.XLOOKUP(D107&amp;"-"&amp;E107,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>235</v>
+      </c>
+      <c r="N107" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O107" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -8764,10 +12218,13 @@
       <c r="L108" s="12">
         <v>2675690</v>
       </c>
-      <c r="M108" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N108" s="14"/>
+      <c r="M108" s="13">
+        <f>+_xlfn.XLOOKUP(D108&amp;"-"&amp;E108,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N108" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O108" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -8833,10 +12290,13 @@
       <c r="L109" s="12">
         <v>2675690</v>
       </c>
-      <c r="M109" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N109" s="14"/>
+      <c r="M109" s="13">
+        <f>+_xlfn.XLOOKUP(D109&amp;"-"&amp;E109,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N109" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O109" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -8902,10 +12362,13 @@
       <c r="L110" s="12">
         <v>2675690</v>
       </c>
-      <c r="M110" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N110" s="14"/>
+      <c r="M110" s="13">
+        <f>+_xlfn.XLOOKUP(D110&amp;"-"&amp;E110,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N110" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O110" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -8971,10 +12434,13 @@
       <c r="L111" s="12">
         <v>2675690</v>
       </c>
-      <c r="M111" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N111" s="14"/>
+      <c r="M111" s="13">
+        <f>+_xlfn.XLOOKUP(D111&amp;"-"&amp;E111,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N111" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O111" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -9040,10 +12506,13 @@
       <c r="L112" s="12">
         <v>2675690</v>
       </c>
-      <c r="M112" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N112" s="14"/>
+      <c r="M112" s="13">
+        <f>+_xlfn.XLOOKUP(D112&amp;"-"&amp;E112,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N112" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O112" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -9109,10 +12578,13 @@
       <c r="L113" s="12">
         <v>2675690</v>
       </c>
-      <c r="M113" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N113" s="14"/>
+      <c r="M113" s="13">
+        <f>+_xlfn.XLOOKUP(D113&amp;"-"&amp;E113,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N113" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O113" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -9178,10 +12650,13 @@
       <c r="L114" s="12">
         <v>2675690</v>
       </c>
-      <c r="M114" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N114" s="14"/>
+      <c r="M114" s="13">
+        <f>+_xlfn.XLOOKUP(D114&amp;"-"&amp;E114,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N114" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O114" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -9247,10 +12722,13 @@
       <c r="L115" s="12">
         <v>2675690</v>
       </c>
-      <c r="M115" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N115" s="14"/>
+      <c r="M115" s="13">
+        <f>+_xlfn.XLOOKUP(D115&amp;"-"&amp;E115,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N115" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O115" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -9316,10 +12794,13 @@
       <c r="L116" s="12">
         <v>1873593</v>
       </c>
-      <c r="M116" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N116" s="14"/>
+      <c r="M116" s="13">
+        <f>+_xlfn.XLOOKUP(D116&amp;"-"&amp;E116,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>235</v>
+      </c>
+      <c r="N116" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O116" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -9385,10 +12866,13 @@
       <c r="L117" s="12">
         <v>2440026</v>
       </c>
-      <c r="M117" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N117" s="14"/>
+      <c r="M117" s="13">
+        <f>+_xlfn.XLOOKUP(D117&amp;"-"&amp;E117,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N117" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O117" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -9454,10 +12938,13 @@
       <c r="L118" s="12">
         <v>1865606</v>
       </c>
-      <c r="M118" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N118" s="14"/>
+      <c r="M118" s="13">
+        <f>+_xlfn.XLOOKUP(D118&amp;"-"&amp;E118,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N118" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O118" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -9523,10 +13010,13 @@
       <c r="L119" s="12">
         <v>1865606</v>
       </c>
-      <c r="M119" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N119" s="14"/>
+      <c r="M119" s="13">
+        <f>+_xlfn.XLOOKUP(D119&amp;"-"&amp;E119,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N119" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O119" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -9592,10 +13082,13 @@
       <c r="L120" s="12">
         <v>1865606</v>
       </c>
-      <c r="M120" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N120" s="14"/>
+      <c r="M120" s="13">
+        <f>+_xlfn.XLOOKUP(D120&amp;"-"&amp;E120,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N120" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O120" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -9661,10 +13154,13 @@
       <c r="L121" s="12">
         <v>1865606</v>
       </c>
-      <c r="M121" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N121" s="14"/>
+      <c r="M121" s="13">
+        <f>+_xlfn.XLOOKUP(D121&amp;"-"&amp;E121,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N121" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O121" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -9730,10 +13226,13 @@
       <c r="L122" s="12">
         <v>2440026</v>
       </c>
-      <c r="M122" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N122" s="14"/>
+      <c r="M122" s="13">
+        <f>+_xlfn.XLOOKUP(D122&amp;"-"&amp;E122,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N122" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O122" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -9799,10 +13298,13 @@
       <c r="L123" s="12">
         <v>2227878</v>
       </c>
-      <c r="M123" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N123" s="14"/>
+      <c r="M123" s="13">
+        <f>+_xlfn.XLOOKUP(D123&amp;"-"&amp;E123,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N123" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O123" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -9868,10 +13370,13 @@
       <c r="L124" s="12">
         <v>2227878</v>
       </c>
-      <c r="M124" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N124" s="14"/>
+      <c r="M124" s="13">
+        <f>+_xlfn.XLOOKUP(D124&amp;"-"&amp;E124,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N124" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O124" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -9937,10 +13442,13 @@
       <c r="L125" s="12">
         <v>2227878</v>
       </c>
-      <c r="M125" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N125" s="14"/>
+      <c r="M125" s="13">
+        <f>+_xlfn.XLOOKUP(D125&amp;"-"&amp;E125,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N125" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O125" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -10006,10 +13514,13 @@
       <c r="L126" s="12">
         <v>2227878</v>
       </c>
-      <c r="M126" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N126" s="14"/>
+      <c r="M126" s="13">
+        <f>+_xlfn.XLOOKUP(D126&amp;"-"&amp;E126,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N126" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O126" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -10075,10 +13586,13 @@
       <c r="L127" s="12">
         <v>2227878</v>
       </c>
-      <c r="M127" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N127" s="14"/>
+      <c r="M127" s="13">
+        <f>+_xlfn.XLOOKUP(D127&amp;"-"&amp;E127,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N127" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O127" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -10144,10 +13658,13 @@
       <c r="L128" s="12">
         <v>2227878</v>
       </c>
-      <c r="M128" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N128" s="14"/>
+      <c r="M128" s="13">
+        <f>+_xlfn.XLOOKUP(D128&amp;"-"&amp;E128,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N128" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O128" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -10213,10 +13730,13 @@
       <c r="L129" s="12">
         <v>2227878</v>
       </c>
-      <c r="M129" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N129" s="14"/>
+      <c r="M129" s="13">
+        <f>+_xlfn.XLOOKUP(D129&amp;"-"&amp;E129,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N129" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O129" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -10282,10 +13802,13 @@
       <c r="L130" s="12">
         <v>2227878</v>
       </c>
-      <c r="M130" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N130" s="14"/>
+      <c r="M130" s="13">
+        <f>+_xlfn.XLOOKUP(D130&amp;"-"&amp;E130,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N130" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O130" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -10351,10 +13874,13 @@
       <c r="L131" s="12">
         <v>2440026</v>
       </c>
-      <c r="M131" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N131" s="14"/>
+      <c r="M131" s="13">
+        <f>+_xlfn.XLOOKUP(D131&amp;"-"&amp;E131,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N131" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O131" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -10420,10 +13946,13 @@
       <c r="L132" s="12">
         <v>1865606</v>
       </c>
-      <c r="M132" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N132" s="14"/>
+      <c r="M132" s="13">
+        <f>+_xlfn.XLOOKUP(D132&amp;"-"&amp;E132,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N132" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O132" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -10489,10 +14018,13 @@
       <c r="L133" s="12">
         <v>1865606</v>
       </c>
-      <c r="M133" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N133" s="14"/>
+      <c r="M133" s="13">
+        <f>+_xlfn.XLOOKUP(D133&amp;"-"&amp;E133,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N133" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O133" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -10558,10 +14090,13 @@
       <c r="L134" s="12">
         <v>1865606</v>
       </c>
-      <c r="M134" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N134" s="14"/>
+      <c r="M134" s="13">
+        <f>+_xlfn.XLOOKUP(D134&amp;"-"&amp;E134,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N134" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O134" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -10627,10 +14162,13 @@
       <c r="L135" s="12">
         <v>1865606</v>
       </c>
-      <c r="M135" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N135" s="14"/>
+      <c r="M135" s="13">
+        <f>+_xlfn.XLOOKUP(D135&amp;"-"&amp;E135,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N135" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O135" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -10696,10 +14234,13 @@
       <c r="L136" s="12">
         <v>2440026</v>
       </c>
-      <c r="M136" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N136" s="14"/>
+      <c r="M136" s="13">
+        <f>+_xlfn.XLOOKUP(D136&amp;"-"&amp;E136,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N136" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O136" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -10765,10 +14306,13 @@
       <c r="L137" s="12">
         <v>2227878</v>
       </c>
-      <c r="M137" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N137" s="14"/>
+      <c r="M137" s="13">
+        <f>+_xlfn.XLOOKUP(D137&amp;"-"&amp;E137,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N137" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O137" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -10834,10 +14378,13 @@
       <c r="L138" s="12">
         <v>2227878</v>
       </c>
-      <c r="M138" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N138" s="14"/>
+      <c r="M138" s="13">
+        <f>+_xlfn.XLOOKUP(D138&amp;"-"&amp;E138,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N138" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O138" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -10903,10 +14450,13 @@
       <c r="L139" s="12">
         <v>2227878</v>
       </c>
-      <c r="M139" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N139" s="14"/>
+      <c r="M139" s="13">
+        <f>+_xlfn.XLOOKUP(D139&amp;"-"&amp;E139,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N139" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O139" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -10972,10 +14522,13 @@
       <c r="L140" s="12">
         <v>2227878</v>
       </c>
-      <c r="M140" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N140" s="14"/>
+      <c r="M140" s="13">
+        <f>+_xlfn.XLOOKUP(D140&amp;"-"&amp;E140,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N140" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O140" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -11041,10 +14594,13 @@
       <c r="L141" s="12">
         <v>2227878</v>
       </c>
-      <c r="M141" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N141" s="14"/>
+      <c r="M141" s="13">
+        <f>+_xlfn.XLOOKUP(D141&amp;"-"&amp;E141,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N141" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O141" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -11110,10 +14666,13 @@
       <c r="L142" s="12">
         <v>2227878</v>
       </c>
-      <c r="M142" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N142" s="14"/>
+      <c r="M142" s="13">
+        <f>+_xlfn.XLOOKUP(D142&amp;"-"&amp;E142,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N142" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O142" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -11179,10 +14738,13 @@
       <c r="L143" s="12">
         <v>2227878</v>
       </c>
-      <c r="M143" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N143" s="14"/>
+      <c r="M143" s="13">
+        <f>+_xlfn.XLOOKUP(D143&amp;"-"&amp;E143,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N143" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O143" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -11248,10 +14810,13 @@
       <c r="L144" s="12">
         <v>2227878</v>
       </c>
-      <c r="M144" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N144" s="14"/>
+      <c r="M144" s="13">
+        <f>+_xlfn.XLOOKUP(D144&amp;"-"&amp;E144,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N144" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O144" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -11318,7 +14883,8 @@
         <v>2320570</v>
       </c>
       <c r="M145" s="13">
-        <v>229</v>
+        <f>+_xlfn.XLOOKUP(D145&amp;"-"&amp;E145,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
       </c>
       <c r="N145" s="20" t="s">
         <v>24</v>
@@ -11393,7 +14959,8 @@
         <v>1865606</v>
       </c>
       <c r="M146" s="13">
-        <v>234</v>
+        <f>+_xlfn.XLOOKUP(D146&amp;"-"&amp;E146,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
       </c>
       <c r="N146" s="20" t="s">
         <v>24</v>
@@ -11468,7 +15035,8 @@
         <v>1865606</v>
       </c>
       <c r="M147" s="13">
-        <v>234</v>
+        <f>+_xlfn.XLOOKUP(D147&amp;"-"&amp;E147,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
       </c>
       <c r="N147" s="20" t="s">
         <v>24</v>
@@ -11543,7 +15111,8 @@
         <v>1865606</v>
       </c>
       <c r="M148" s="13">
-        <v>234</v>
+        <f>+_xlfn.XLOOKUP(D148&amp;"-"&amp;E148,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
       </c>
       <c r="N148" s="20" t="s">
         <v>24</v>
@@ -11618,7 +15187,8 @@
         <v>1865606</v>
       </c>
       <c r="M149" s="13">
-        <v>234</v>
+        <f>+_xlfn.XLOOKUP(D149&amp;"-"&amp;E149,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
       </c>
       <c r="N149" s="20" t="s">
         <v>24</v>
@@ -11693,7 +15263,8 @@
         <v>2320570</v>
       </c>
       <c r="M150" s="13">
-        <v>229</v>
+        <f>+_xlfn.XLOOKUP(D150&amp;"-"&amp;E150,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
       </c>
       <c r="N150" s="20" t="s">
         <v>24</v>
@@ -11768,7 +15339,8 @@
         <v>2227878</v>
       </c>
       <c r="M151" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D151&amp;"-"&amp;E151,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N151" s="20" t="s">
         <v>24</v>
@@ -11843,7 +15415,8 @@
         <v>2227878</v>
       </c>
       <c r="M152" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D152&amp;"-"&amp;E152,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N152" s="20" t="s">
         <v>24</v>
@@ -11918,7 +15491,8 @@
         <v>2227878</v>
       </c>
       <c r="M153" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D153&amp;"-"&amp;E153,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N153" s="20" t="s">
         <v>24</v>
@@ -11993,7 +15567,8 @@
         <v>2227878</v>
       </c>
       <c r="M154" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D154&amp;"-"&amp;E154,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N154" s="20" t="s">
         <v>24</v>
@@ -12068,7 +15643,8 @@
         <v>2227878</v>
       </c>
       <c r="M155" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D155&amp;"-"&amp;E155,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N155" s="20" t="s">
         <v>24</v>
@@ -12143,7 +15719,8 @@
         <v>2227878</v>
       </c>
       <c r="M156" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D156&amp;"-"&amp;E156,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N156" s="20" t="s">
         <v>24</v>
@@ -12218,7 +15795,8 @@
         <v>2227878</v>
       </c>
       <c r="M157" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D157&amp;"-"&amp;E157,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N157" s="27" t="s">
         <v>42</v>
@@ -12293,7 +15871,8 @@
         <v>2227878</v>
       </c>
       <c r="M158" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D158&amp;"-"&amp;E158,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N158" s="20" t="s">
         <v>24</v>
@@ -12368,10 +15947,11 @@
         <v>2158434</v>
       </c>
       <c r="M159" s="13">
-        <v>229</v>
+        <f>+_xlfn.XLOOKUP(D159&amp;"-"&amp;E159,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>213.22</v>
       </c>
       <c r="N159" s="28" t="s">
-        <v>45</v>
+        <v>233</v>
       </c>
       <c r="O159" s="14">
         <v>0</v>
@@ -12443,7 +16023,8 @@
         <v>1865606</v>
       </c>
       <c r="M160" s="13">
-        <v>234</v>
+        <f>+_xlfn.XLOOKUP(D160&amp;"-"&amp;E160,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
       </c>
       <c r="N160" s="28" t="s">
         <v>45</v>
@@ -12518,7 +16099,8 @@
         <v>1865606</v>
       </c>
       <c r="M161" s="13">
-        <v>234</v>
+        <f>+_xlfn.XLOOKUP(D161&amp;"-"&amp;E161,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
       </c>
       <c r="N161" s="28" t="s">
         <v>45</v>
@@ -12593,7 +16175,8 @@
         <v>1865606</v>
       </c>
       <c r="M162" s="13">
-        <v>234</v>
+        <f>+_xlfn.XLOOKUP(D162&amp;"-"&amp;E162,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
       </c>
       <c r="N162" s="28" t="s">
         <v>45</v>
@@ -12668,7 +16251,8 @@
         <v>1865606</v>
       </c>
       <c r="M163" s="13">
-        <v>234</v>
+        <f>+_xlfn.XLOOKUP(D163&amp;"-"&amp;E163,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
       </c>
       <c r="N163" s="28" t="s">
         <v>45</v>
@@ -12743,7 +16327,8 @@
         <v>2320570</v>
       </c>
       <c r="M164" s="13">
-        <v>229</v>
+        <f>+_xlfn.XLOOKUP(D164&amp;"-"&amp;E164,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
       </c>
       <c r="N164" s="28" t="s">
         <v>45</v>
@@ -12818,7 +16403,8 @@
         <v>2227878</v>
       </c>
       <c r="M165" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D165&amp;"-"&amp;E165,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N165" s="20" t="s">
         <v>24</v>
@@ -12893,7 +16479,8 @@
         <v>2227878</v>
       </c>
       <c r="M166" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D166&amp;"-"&amp;E166,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N166" s="20" t="s">
         <v>24</v>
@@ -12968,7 +16555,8 @@
         <v>2227878</v>
       </c>
       <c r="M167" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D167&amp;"-"&amp;E167,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N167" s="20" t="s">
         <v>24</v>
@@ -13043,7 +16631,8 @@
         <v>2227878</v>
       </c>
       <c r="M168" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D168&amp;"-"&amp;E168,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N168" s="20" t="s">
         <v>24</v>
@@ -13118,7 +16707,8 @@
         <v>2227878</v>
       </c>
       <c r="M169" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D169&amp;"-"&amp;E169,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N169" s="20" t="s">
         <v>24</v>
@@ -13193,7 +16783,8 @@
         <v>2227878</v>
       </c>
       <c r="M170" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D170&amp;"-"&amp;E170,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N170" s="20" t="s">
         <v>24</v>
@@ -13268,7 +16859,8 @@
         <v>2227878</v>
       </c>
       <c r="M171" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D171&amp;"-"&amp;E171,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N171" s="20" t="s">
         <v>24</v>
@@ -13343,7 +16935,8 @@
         <v>2227878</v>
       </c>
       <c r="M172" s="13">
-        <v>299</v>
+        <f>+_xlfn.XLOOKUP(D172&amp;"-"&amp;E172,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
       </c>
       <c r="N172" s="20" t="s">
         <v>24</v>
@@ -13417,10 +17010,13 @@
       <c r="L173" s="12">
         <v>2551256</v>
       </c>
-      <c r="M173" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N173" s="14"/>
+      <c r="M173" s="13">
+        <f>+_xlfn.XLOOKUP(D173&amp;"-"&amp;E173,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>214.24</v>
+      </c>
+      <c r="N173" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O173" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -13486,10 +17082,13 @@
       <c r="L174" s="12">
         <v>1865606</v>
       </c>
-      <c r="M174" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N174" s="14"/>
+      <c r="M174" s="13">
+        <f>+_xlfn.XLOOKUP(D174&amp;"-"&amp;E174,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N174" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O174" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -13555,10 +17154,13 @@
       <c r="L175" s="12">
         <v>1865606</v>
       </c>
-      <c r="M175" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N175" s="14"/>
+      <c r="M175" s="13">
+        <f>+_xlfn.XLOOKUP(D175&amp;"-"&amp;E175,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N175" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O175" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -13624,10 +17226,13 @@
       <c r="L176" s="12">
         <v>1865606</v>
       </c>
-      <c r="M176" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N176" s="14"/>
+      <c r="M176" s="13">
+        <f>+_xlfn.XLOOKUP(D176&amp;"-"&amp;E176,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N176" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O176" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -13693,10 +17298,13 @@
       <c r="L177" s="12">
         <v>1865606</v>
       </c>
-      <c r="M177" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N177" s="14"/>
+      <c r="M177" s="13">
+        <f>+_xlfn.XLOOKUP(D177&amp;"-"&amp;E177,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N177" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O177" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -13762,10 +17370,13 @@
       <c r="L178" s="12">
         <v>1865606</v>
       </c>
-      <c r="M178" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N178" s="14"/>
+      <c r="M178" s="13">
+        <f>+_xlfn.XLOOKUP(D178&amp;"-"&amp;E178,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N178" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O178" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -13831,10 +17442,13 @@
       <c r="L179" s="12">
         <v>2320570</v>
       </c>
-      <c r="M179" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N179" s="14"/>
+      <c r="M179" s="13">
+        <f>+_xlfn.XLOOKUP(D179&amp;"-"&amp;E179,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N179" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O179" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -13900,10 +17514,13 @@
       <c r="L180" s="12">
         <v>2668984</v>
       </c>
-      <c r="M180" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N180" s="14"/>
+      <c r="M180" s="13">
+        <f>+_xlfn.XLOOKUP(D180&amp;"-"&amp;E180,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N180" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O180" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -13969,10 +17586,13 @@
       <c r="L181" s="12">
         <v>2668984</v>
       </c>
-      <c r="M181" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N181" s="14"/>
+      <c r="M181" s="13">
+        <f>+_xlfn.XLOOKUP(D181&amp;"-"&amp;E181,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N181" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O181" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -14038,10 +17658,13 @@
       <c r="L182" s="12">
         <v>2668984</v>
       </c>
-      <c r="M182" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N182" s="14"/>
+      <c r="M182" s="13">
+        <f>+_xlfn.XLOOKUP(D182&amp;"-"&amp;E182,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N182" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O182" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -14107,10 +17730,13 @@
       <c r="L183" s="12">
         <v>2668984</v>
       </c>
-      <c r="M183" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N183" s="14"/>
+      <c r="M183" s="13">
+        <f>+_xlfn.XLOOKUP(D183&amp;"-"&amp;E183,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N183" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O183" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -14176,10 +17802,13 @@
       <c r="L184" s="12">
         <v>2668984</v>
       </c>
-      <c r="M184" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N184" s="14"/>
+      <c r="M184" s="13">
+        <f>+_xlfn.XLOOKUP(D184&amp;"-"&amp;E184,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N184" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O184" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -14245,10 +17874,13 @@
       <c r="L185" s="12">
         <v>2668984</v>
       </c>
-      <c r="M185" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N185" s="14"/>
+      <c r="M185" s="13">
+        <f>+_xlfn.XLOOKUP(D185&amp;"-"&amp;E185,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N185" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O185" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -14314,10 +17946,13 @@
       <c r="L186" s="12">
         <v>2668984</v>
       </c>
-      <c r="M186" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N186" s="14"/>
+      <c r="M186" s="13">
+        <f>+_xlfn.XLOOKUP(D186&amp;"-"&amp;E186,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N186" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O186" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -14383,10 +18018,13 @@
       <c r="L187" s="12">
         <v>2668984</v>
       </c>
-      <c r="M187" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N187" s="14"/>
+      <c r="M187" s="13">
+        <f>+_xlfn.XLOOKUP(D187&amp;"-"&amp;E187,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N187" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O187" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -14452,10 +18090,13 @@
       <c r="L188" s="12">
         <v>2320570</v>
       </c>
-      <c r="M188" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N188" s="14"/>
+      <c r="M188" s="13">
+        <f>+_xlfn.XLOOKUP(D188&amp;"-"&amp;E188,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N188" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O188" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -14521,10 +18162,13 @@
       <c r="L189" s="12">
         <v>1865606</v>
       </c>
-      <c r="M189" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N189" s="14"/>
+      <c r="M189" s="13">
+        <f>+_xlfn.XLOOKUP(D189&amp;"-"&amp;E189,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N189" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O189" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -14590,10 +18234,13 @@
       <c r="L190" s="12">
         <v>1865606</v>
       </c>
-      <c r="M190" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N190" s="14"/>
+      <c r="M190" s="13">
+        <f>+_xlfn.XLOOKUP(D190&amp;"-"&amp;E190,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N190" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O190" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -14659,10 +18306,13 @@
       <c r="L191" s="12">
         <v>1865606</v>
       </c>
-      <c r="M191" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N191" s="14"/>
+      <c r="M191" s="13">
+        <f>+_xlfn.XLOOKUP(D191&amp;"-"&amp;E191,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N191" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O191" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -14728,10 +18378,13 @@
       <c r="L192" s="12">
         <v>1865606</v>
       </c>
-      <c r="M192" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N192" s="14"/>
+      <c r="M192" s="13">
+        <f>+_xlfn.XLOOKUP(D192&amp;"-"&amp;E192,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N192" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O192" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -14797,10 +18450,13 @@
       <c r="L193" s="12">
         <v>1865606</v>
       </c>
-      <c r="M193" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N193" s="14"/>
+      <c r="M193" s="13">
+        <f>+_xlfn.XLOOKUP(D193&amp;"-"&amp;E193,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N193" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O193" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -14866,10 +18522,13 @@
       <c r="L194" s="12">
         <v>2753926</v>
       </c>
-      <c r="M194" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N194" s="14"/>
+      <c r="M194" s="13">
+        <f>+_xlfn.XLOOKUP(D194&amp;"-"&amp;E194,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>230.52</v>
+      </c>
+      <c r="N194" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O194" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -14935,10 +18594,13 @@
       <c r="L195" s="12">
         <v>2013674</v>
       </c>
-      <c r="M195" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N195" s="14"/>
+      <c r="M195" s="13">
+        <f>+_xlfn.XLOOKUP(D195&amp;"-"&amp;E195,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>235</v>
+      </c>
+      <c r="N195" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O195" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -15004,10 +18666,13 @@
       <c r="L196" s="12">
         <v>2675690</v>
       </c>
-      <c r="M196" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N196" s="14"/>
+      <c r="M196" s="13">
+        <f>+_xlfn.XLOOKUP(D196&amp;"-"&amp;E196,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N196" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O196" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -15073,10 +18738,13 @@
       <c r="L197" s="12">
         <v>2675690</v>
       </c>
-      <c r="M197" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N197" s="14"/>
+      <c r="M197" s="13">
+        <f>+_xlfn.XLOOKUP(D197&amp;"-"&amp;E197,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N197" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O197" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -15142,10 +18810,13 @@
       <c r="L198" s="12">
         <v>2675690</v>
       </c>
-      <c r="M198" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N198" s="14"/>
+      <c r="M198" s="13">
+        <f>+_xlfn.XLOOKUP(D198&amp;"-"&amp;E198,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N198" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O198" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -15211,10 +18882,13 @@
       <c r="L199" s="12">
         <v>2675690</v>
       </c>
-      <c r="M199" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N199" s="14"/>
+      <c r="M199" s="13">
+        <f>+_xlfn.XLOOKUP(D199&amp;"-"&amp;E199,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N199" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O199" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -15280,10 +18954,13 @@
       <c r="L200" s="12">
         <v>2675690</v>
       </c>
-      <c r="M200" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N200" s="14"/>
+      <c r="M200" s="13">
+        <f>+_xlfn.XLOOKUP(D200&amp;"-"&amp;E200,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N200" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O200" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -15349,10 +19026,13 @@
       <c r="L201" s="12">
         <v>2675690</v>
       </c>
-      <c r="M201" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N201" s="14"/>
+      <c r="M201" s="13">
+        <f>+_xlfn.XLOOKUP(D201&amp;"-"&amp;E201,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N201" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O201" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -15418,10 +19098,13 @@
       <c r="L202" s="12">
         <v>2675690</v>
       </c>
-      <c r="M202" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N202" s="14"/>
+      <c r="M202" s="13">
+        <f>+_xlfn.XLOOKUP(D202&amp;"-"&amp;E202,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N202" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O202" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -15487,10 +19170,13 @@
       <c r="L203" s="12">
         <v>2675690</v>
       </c>
-      <c r="M203" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N203" s="14"/>
+      <c r="M203" s="13">
+        <f>+_xlfn.XLOOKUP(D203&amp;"-"&amp;E203,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N203" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O203" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -15556,10 +19242,13 @@
       <c r="L204" s="12">
         <v>2013674</v>
       </c>
-      <c r="M204" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N204" s="14"/>
+      <c r="M204" s="13">
+        <f>+_xlfn.XLOOKUP(D204&amp;"-"&amp;E204,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>235</v>
+      </c>
+      <c r="N204" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O204" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -15625,10 +19314,13 @@
       <c r="L205" s="12">
         <v>1848170</v>
       </c>
-      <c r="M205" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N205" s="14"/>
+      <c r="M205" s="13">
+        <f>+_xlfn.XLOOKUP(D205&amp;"-"&amp;E205,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N205" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O205" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -15694,10 +19386,13 @@
       <c r="L206" s="12">
         <v>1848170</v>
       </c>
-      <c r="M206" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N206" s="14"/>
+      <c r="M206" s="13">
+        <f>+_xlfn.XLOOKUP(D206&amp;"-"&amp;E206,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N206" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O206" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -15763,10 +19458,13 @@
       <c r="L207" s="12">
         <v>1813299</v>
       </c>
-      <c r="M207" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N207" s="14"/>
+      <c r="M207" s="13">
+        <f>+_xlfn.XLOOKUP(D207&amp;"-"&amp;E207,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N207" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O207" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -15832,10 +19530,13 @@
       <c r="L208" s="12">
         <v>1917913</v>
       </c>
-      <c r="M208" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N208" s="14"/>
+      <c r="M208" s="13">
+        <f>+_xlfn.XLOOKUP(D208&amp;"-"&amp;E208,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N208" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O208" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -15901,10 +19602,13 @@
       <c r="L209" s="12">
         <v>2330704</v>
       </c>
-      <c r="M209" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N209" s="14"/>
+      <c r="M209" s="13">
+        <f>+_xlfn.XLOOKUP(D209&amp;"-"&amp;E209,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N209" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O209" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -15970,10 +19674,13 @@
       <c r="L210" s="12">
         <v>2227878</v>
       </c>
-      <c r="M210" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N210" s="14"/>
+      <c r="M210" s="13">
+        <f>+_xlfn.XLOOKUP(D210&amp;"-"&amp;E210,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N210" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O210" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -16039,10 +19746,13 @@
       <c r="L211" s="12">
         <v>2183321</v>
       </c>
-      <c r="M211" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N211" s="14"/>
+      <c r="M211" s="13">
+        <f>+_xlfn.XLOOKUP(D211&amp;"-"&amp;E211,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N211" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O211" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -16108,10 +19818,13 @@
       <c r="L212" s="12">
         <v>2183321</v>
       </c>
-      <c r="M212" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N212" s="14"/>
+      <c r="M212" s="13">
+        <f>+_xlfn.XLOOKUP(D212&amp;"-"&amp;E212,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N212" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O212" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -16177,10 +19890,13 @@
       <c r="L213" s="12">
         <v>2183321</v>
       </c>
-      <c r="M213" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N213" s="14"/>
+      <c r="M213" s="13">
+        <f>+_xlfn.XLOOKUP(D213&amp;"-"&amp;E213,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N213" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O213" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -16246,10 +19962,13 @@
       <c r="L214" s="12">
         <v>2183321</v>
       </c>
-      <c r="M214" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N214" s="14"/>
+      <c r="M214" s="13">
+        <f>+_xlfn.XLOOKUP(D214&amp;"-"&amp;E214,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N214" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O214" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -16315,10 +20034,13 @@
       <c r="L215" s="12">
         <v>2227878</v>
       </c>
-      <c r="M215" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N215" s="14"/>
+      <c r="M215" s="13">
+        <f>+_xlfn.XLOOKUP(D215&amp;"-"&amp;E215,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N215" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O215" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -16384,10 +20106,13 @@
       <c r="L216" s="12">
         <v>2183321</v>
       </c>
-      <c r="M216" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N216" s="14"/>
+      <c r="M216" s="13">
+        <f>+_xlfn.XLOOKUP(D216&amp;"-"&amp;E216,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N216" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O216" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -16453,10 +20178,13 @@
       <c r="L217" s="12">
         <v>2183321</v>
       </c>
-      <c r="M217" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N217" s="14"/>
+      <c r="M217" s="13">
+        <f>+_xlfn.XLOOKUP(D217&amp;"-"&amp;E217,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N217" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O217" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -16522,10 +20250,13 @@
       <c r="L218" s="12">
         <v>2320570</v>
       </c>
-      <c r="M218" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N218" s="14"/>
+      <c r="M218" s="13">
+        <f>+_xlfn.XLOOKUP(D218&amp;"-"&amp;E218,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N218" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O218" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -16591,10 +20322,13 @@
       <c r="L219" s="12">
         <v>1848170</v>
       </c>
-      <c r="M219" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N219" s="14"/>
+      <c r="M219" s="13">
+        <f>+_xlfn.XLOOKUP(D219&amp;"-"&amp;E219,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N219" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O219" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -16660,10 +20394,13 @@
       <c r="L220" s="12">
         <v>1935348</v>
       </c>
-      <c r="M220" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N220" s="14"/>
+      <c r="M220" s="13">
+        <f>+_xlfn.XLOOKUP(D220&amp;"-"&amp;E220,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N220" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O220" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -16729,10 +20466,13 @@
       <c r="L221" s="12">
         <v>1813299</v>
       </c>
-      <c r="M221" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N221" s="14"/>
+      <c r="M221" s="13">
+        <f>+_xlfn.XLOOKUP(D221&amp;"-"&amp;E221,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N221" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O221" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -16798,10 +20538,13 @@
       <c r="L222" s="12">
         <v>1848170</v>
       </c>
-      <c r="M222" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N222" s="14"/>
+      <c r="M222" s="13">
+        <f>+_xlfn.XLOOKUP(D222&amp;"-"&amp;E222,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N222" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O222" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -16867,10 +20610,13 @@
       <c r="L223" s="12">
         <v>28727090</v>
       </c>
-      <c r="M223" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N223" s="14"/>
+      <c r="M223" s="13">
+        <f>+_xlfn.XLOOKUP(D223&amp;"-"&amp;E223,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N223" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O223" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -16936,10 +20682,13 @@
       <c r="L224" s="12">
         <v>2205585</v>
       </c>
-      <c r="M224" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N224" s="14"/>
+      <c r="M224" s="13">
+        <f>+_xlfn.XLOOKUP(D224&amp;"-"&amp;E224,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N224" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O224" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -17005,10 +20754,13 @@
       <c r="L225" s="12">
         <v>2161027</v>
       </c>
-      <c r="M225" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N225" s="14"/>
+      <c r="M225" s="13">
+        <f>+_xlfn.XLOOKUP(D225&amp;"-"&amp;E225,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N225" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O225" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -17074,10 +20826,13 @@
       <c r="L226" s="12">
         <v>2250142</v>
       </c>
-      <c r="M226" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N226" s="14"/>
+      <c r="M226" s="13">
+        <f>+_xlfn.XLOOKUP(D226&amp;"-"&amp;E226,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N226" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O226" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -17143,10 +20898,13 @@
       <c r="L227" s="12">
         <v>2205585</v>
       </c>
-      <c r="M227" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N227" s="14"/>
+      <c r="M227" s="13">
+        <f>+_xlfn.XLOOKUP(D227&amp;"-"&amp;E227,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N227" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O227" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -17212,10 +20970,13 @@
       <c r="L228" s="12">
         <v>2250142</v>
       </c>
-      <c r="M228" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N228" s="14"/>
+      <c r="M228" s="13">
+        <f>+_xlfn.XLOOKUP(D228&amp;"-"&amp;E228,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N228" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O228" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -17281,10 +21042,13 @@
       <c r="L229" s="12">
         <v>2183321</v>
       </c>
-      <c r="M229" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N229" s="14"/>
+      <c r="M229" s="13">
+        <f>+_xlfn.XLOOKUP(D229&amp;"-"&amp;E229,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N229" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O229" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -17350,10 +21114,13 @@
       <c r="L230" s="12">
         <v>2138763</v>
       </c>
-      <c r="M230" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N230" s="14"/>
+      <c r="M230" s="13">
+        <f>+_xlfn.XLOOKUP(D230&amp;"-"&amp;E230,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N230" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O230" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -17419,10 +21186,13 @@
       <c r="L231" s="12">
         <v>2183321</v>
       </c>
-      <c r="M231" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N231" s="14"/>
+      <c r="M231" s="13">
+        <f>+_xlfn.XLOOKUP(D231&amp;"-"&amp;E231,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N231" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O231" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -17486,10 +21256,13 @@
         <v>89</v>
       </c>
       <c r="L232" s="30"/>
-      <c r="M232" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N232" s="14"/>
+      <c r="M232" s="13">
+        <f>+_xlfn.XLOOKUP(D232&amp;"-"&amp;E232,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N232" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O232" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -17551,10 +21324,13 @@
       </c>
       <c r="K233" s="11"/>
       <c r="L233" s="30"/>
-      <c r="M233" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N233" s="14"/>
+      <c r="M233" s="13">
+        <f>+_xlfn.XLOOKUP(D233&amp;"-"&amp;E233,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N233" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O233" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -17616,10 +21392,13 @@
       </c>
       <c r="K234" s="11"/>
       <c r="L234" s="30"/>
-      <c r="M234" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N234" s="14"/>
+      <c r="M234" s="13">
+        <f>+_xlfn.XLOOKUP(D234&amp;"-"&amp;E234,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N234" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O234" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -17681,10 +21460,13 @@
       </c>
       <c r="K235" s="11"/>
       <c r="L235" s="30"/>
-      <c r="M235" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N235" s="14"/>
+      <c r="M235" s="13">
+        <f>+_xlfn.XLOOKUP(D235&amp;"-"&amp;E235,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N235" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O235" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -17746,10 +21528,13 @@
       </c>
       <c r="K236" s="11"/>
       <c r="L236" s="30"/>
-      <c r="M236" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N236" s="14"/>
+      <c r="M236" s="13">
+        <f>+_xlfn.XLOOKUP(D236&amp;"-"&amp;E236,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N236" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O236" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -17811,10 +21596,13 @@
       </c>
       <c r="K237" s="11"/>
       <c r="L237" s="30"/>
-      <c r="M237" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N237" s="14"/>
+      <c r="M237" s="13">
+        <f>+_xlfn.XLOOKUP(D237&amp;"-"&amp;E237,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N237" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O237" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -17876,10 +21664,13 @@
       </c>
       <c r="K238" s="11"/>
       <c r="L238" s="30"/>
-      <c r="M238" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N238" s="14"/>
+      <c r="M238" s="13">
+        <f>+_xlfn.XLOOKUP(D238&amp;"-"&amp;E238,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N238" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O238" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -17941,10 +21732,13 @@
       </c>
       <c r="K239" s="11"/>
       <c r="L239" s="30"/>
-      <c r="M239" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N239" s="14"/>
+      <c r="M239" s="13">
+        <f>+_xlfn.XLOOKUP(D239&amp;"-"&amp;E239,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N239" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O239" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18006,10 +21800,13 @@
       </c>
       <c r="K240" s="11"/>
       <c r="L240" s="30"/>
-      <c r="M240" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N240" s="14"/>
+      <c r="M240" s="13">
+        <f>+_xlfn.XLOOKUP(D240&amp;"-"&amp;E240,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N240" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O240" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18071,10 +21868,13 @@
       </c>
       <c r="K241" s="11"/>
       <c r="L241" s="30"/>
-      <c r="M241" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N241" s="14"/>
+      <c r="M241" s="13">
+        <f>+_xlfn.XLOOKUP(D241&amp;"-"&amp;E241,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N241" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O241" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18136,10 +21936,13 @@
       </c>
       <c r="K242" s="11"/>
       <c r="L242" s="30"/>
-      <c r="M242" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N242" s="14"/>
+      <c r="M242" s="13">
+        <f>+_xlfn.XLOOKUP(D242&amp;"-"&amp;E242,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N242" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O242" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18201,10 +22004,13 @@
       </c>
       <c r="K243" s="11"/>
       <c r="L243" s="30"/>
-      <c r="M243" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N243" s="14"/>
+      <c r="M243" s="13">
+        <f>+_xlfn.XLOOKUP(D243&amp;"-"&amp;E243,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N243" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O243" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18266,10 +22072,13 @@
       </c>
       <c r="K244" s="11"/>
       <c r="L244" s="30"/>
-      <c r="M244" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N244" s="14"/>
+      <c r="M244" s="13">
+        <f>+_xlfn.XLOOKUP(D244&amp;"-"&amp;E244,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N244" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O244" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18331,10 +22140,13 @@
       </c>
       <c r="K245" s="11"/>
       <c r="L245" s="30"/>
-      <c r="M245" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N245" s="14"/>
+      <c r="M245" s="13">
+        <f>+_xlfn.XLOOKUP(D245&amp;"-"&amp;E245,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N245" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O245" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18396,10 +22208,13 @@
       </c>
       <c r="K246" s="11"/>
       <c r="L246" s="30"/>
-      <c r="M246" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N246" s="14"/>
+      <c r="M246" s="13">
+        <f>+_xlfn.XLOOKUP(D246&amp;"-"&amp;E246,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N246" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O246" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18461,10 +22276,13 @@
       </c>
       <c r="K247" s="11"/>
       <c r="L247" s="30"/>
-      <c r="M247" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N247" s="14"/>
+      <c r="M247" s="13">
+        <f>+_xlfn.XLOOKUP(D247&amp;"-"&amp;E247,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N247" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O247" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18528,10 +22346,13 @@
         <v>105</v>
       </c>
       <c r="L248" s="30"/>
-      <c r="M248" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N248" s="14"/>
+      <c r="M248" s="13">
+        <f>+_xlfn.XLOOKUP(D248&amp;"-"&amp;E248,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N248" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O248" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18593,10 +22414,13 @@
       </c>
       <c r="K249" s="11"/>
       <c r="L249" s="30"/>
-      <c r="M249" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N249" s="14"/>
+      <c r="M249" s="13">
+        <f>+_xlfn.XLOOKUP(D249&amp;"-"&amp;E249,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N249" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O249" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18658,10 +22482,13 @@
       </c>
       <c r="K250" s="11"/>
       <c r="L250" s="30"/>
-      <c r="M250" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N250" s="14"/>
+      <c r="M250" s="13">
+        <f>+_xlfn.XLOOKUP(D250&amp;"-"&amp;E250,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N250" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O250" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18723,10 +22550,13 @@
       </c>
       <c r="K251" s="11"/>
       <c r="L251" s="30"/>
-      <c r="M251" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N251" s="14"/>
+      <c r="M251" s="13">
+        <f>+_xlfn.XLOOKUP(D251&amp;"-"&amp;E251,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N251" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O251" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18788,10 +22618,13 @@
       </c>
       <c r="K252" s="11"/>
       <c r="L252" s="30"/>
-      <c r="M252" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N252" s="14"/>
+      <c r="M252" s="13">
+        <f>+_xlfn.XLOOKUP(D252&amp;"-"&amp;E252,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N252" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O252" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18853,10 +22686,13 @@
       </c>
       <c r="K253" s="11"/>
       <c r="L253" s="30"/>
-      <c r="M253" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N253" s="14"/>
+      <c r="M253" s="13">
+        <f>+_xlfn.XLOOKUP(D253&amp;"-"&amp;E253,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N253" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O253" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18918,10 +22754,13 @@
       </c>
       <c r="K254" s="11"/>
       <c r="L254" s="30"/>
-      <c r="M254" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N254" s="14"/>
+      <c r="M254" s="13">
+        <f>+_xlfn.XLOOKUP(D254&amp;"-"&amp;E254,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N254" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O254" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -18983,10 +22822,13 @@
       </c>
       <c r="K255" s="11"/>
       <c r="L255" s="30"/>
-      <c r="M255" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N255" s="14"/>
+      <c r="M255" s="13">
+        <f>+_xlfn.XLOOKUP(D255&amp;"-"&amp;E255,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N255" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O255" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -19048,10 +22890,13 @@
       </c>
       <c r="K256" s="11"/>
       <c r="L256" s="30"/>
-      <c r="M256" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N256" s="14"/>
+      <c r="M256" s="13">
+        <f>+_xlfn.XLOOKUP(D256&amp;"-"&amp;E256,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>398.26</v>
+      </c>
+      <c r="N256" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O256" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -19113,10 +22958,12 @@
       </c>
       <c r="K257" s="11"/>
       <c r="L257" s="30"/>
-      <c r="M257" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N257" s="14"/>
+      <c r="M257" s="13">
+        <v>251</v>
+      </c>
+      <c r="N257" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O257" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -19178,10 +23025,12 @@
       </c>
       <c r="K258" s="11"/>
       <c r="L258" s="30"/>
-      <c r="M258" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N258" s="14"/>
+      <c r="M258" s="13">
+        <v>252</v>
+      </c>
+      <c r="N258" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O258" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -19243,10 +23092,12 @@
       </c>
       <c r="K259" s="11"/>
       <c r="L259" s="30"/>
-      <c r="M259" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N259" s="14"/>
+      <c r="M259" s="13">
+        <v>250</v>
+      </c>
+      <c r="N259" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O259" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -19308,10 +23159,12 @@
       </c>
       <c r="K260" s="11"/>
       <c r="L260" s="30"/>
-      <c r="M260" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N260" s="14"/>
+      <c r="M260" s="13">
+        <v>247</v>
+      </c>
+      <c r="N260" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O260" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -19373,10 +23226,12 @@
       </c>
       <c r="K261" s="11"/>
       <c r="L261" s="30"/>
-      <c r="M261" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N261" s="14"/>
+      <c r="M261" s="13">
+        <v>244</v>
+      </c>
+      <c r="N261" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O261" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -19438,10 +23293,12 @@
       </c>
       <c r="K262" s="11"/>
       <c r="L262" s="30"/>
-      <c r="M262" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N262" s="14"/>
+      <c r="M262" s="13">
+        <v>241</v>
+      </c>
+      <c r="N262" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O262" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -19503,10 +23360,12 @@
       </c>
       <c r="K263" s="11"/>
       <c r="L263" s="30"/>
-      <c r="M263" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N263" s="14"/>
+      <c r="M263" s="13">
+        <v>240</v>
+      </c>
+      <c r="N263" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O263" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -19568,10 +23427,12 @@
       </c>
       <c r="K264" s="11"/>
       <c r="L264" s="30"/>
-      <c r="M264" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N264" s="14"/>
+      <c r="M264" s="13">
+        <v>229</v>
+      </c>
+      <c r="N264" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O264" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -19633,10 +23494,13 @@
       </c>
       <c r="K265" s="11"/>
       <c r="L265" s="30"/>
-      <c r="M265" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N265" s="14"/>
+      <c r="M265" s="13">
+        <f>+_xlfn.XLOOKUP(D265&amp;"-"&amp;E265,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N265" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O265" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -19698,10 +23562,13 @@
       </c>
       <c r="K266" s="11"/>
       <c r="L266" s="30"/>
-      <c r="M266" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N266" s="14"/>
+      <c r="M266" s="13">
+        <f>+_xlfn.XLOOKUP(D266&amp;"-"&amp;E266,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N266" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O266" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -19763,10 +23630,13 @@
       </c>
       <c r="K267" s="11"/>
       <c r="L267" s="30"/>
-      <c r="M267" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N267" s="14"/>
+      <c r="M267" s="13">
+        <f>+_xlfn.XLOOKUP(D267&amp;"-"&amp;E267,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N267" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O267" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -19828,10 +23698,13 @@
       </c>
       <c r="K268" s="11"/>
       <c r="L268" s="30"/>
-      <c r="M268" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N268" s="14"/>
+      <c r="M268" s="13">
+        <f>+_xlfn.XLOOKUP(D268&amp;"-"&amp;E268,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N268" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O268" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -19893,10 +23766,13 @@
       </c>
       <c r="K269" s="11"/>
       <c r="L269" s="30"/>
-      <c r="M269" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N269" s="14"/>
+      <c r="M269" s="13">
+        <f>+_xlfn.XLOOKUP(D269&amp;"-"&amp;E269,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N269" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O269" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -19958,10 +23834,13 @@
       </c>
       <c r="K270" s="11"/>
       <c r="L270" s="30"/>
-      <c r="M270" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N270" s="14"/>
+      <c r="M270" s="13">
+        <f>+_xlfn.XLOOKUP(D270&amp;"-"&amp;E270,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>399.15</v>
+      </c>
+      <c r="N270" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O270" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -20025,10 +23904,13 @@
         <v>136</v>
       </c>
       <c r="L271" s="30"/>
-      <c r="M271" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N271" s="14"/>
+      <c r="M271" s="13">
+        <f>+_xlfn.XLOOKUP(D271&amp;"-"&amp;E271,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N271" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O271" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -20090,10 +23972,13 @@
       </c>
       <c r="K272" s="11"/>
       <c r="L272" s="30"/>
-      <c r="M272" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N272" s="14"/>
+      <c r="M272" s="13">
+        <f>+_xlfn.XLOOKUP(D272&amp;"-"&amp;E272,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N272" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O272" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -20155,10 +24040,13 @@
       </c>
       <c r="K273" s="11"/>
       <c r="L273" s="30"/>
-      <c r="M273" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N273" s="14"/>
+      <c r="M273" s="13">
+        <f>+_xlfn.XLOOKUP(D273&amp;"-"&amp;E273,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N273" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O273" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -20220,10 +24108,13 @@
       </c>
       <c r="K274" s="11"/>
       <c r="L274" s="30"/>
-      <c r="M274" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N274" s="14"/>
+      <c r="M274" s="13">
+        <f>+_xlfn.XLOOKUP(D274&amp;"-"&amp;E274,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N274" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O274" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -20285,10 +24176,13 @@
       </c>
       <c r="K275" s="11"/>
       <c r="L275" s="30"/>
-      <c r="M275" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N275" s="14"/>
+      <c r="M275" s="13">
+        <f>+_xlfn.XLOOKUP(D275&amp;"-"&amp;E275,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N275" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O275" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -20350,10 +24244,13 @@
       </c>
       <c r="K276" s="11"/>
       <c r="L276" s="30"/>
-      <c r="M276" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N276" s="14"/>
+      <c r="M276" s="13">
+        <f>+_xlfn.XLOOKUP(D276&amp;"-"&amp;E276,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N276" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O276" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -20415,10 +24312,13 @@
       </c>
       <c r="K277" s="11"/>
       <c r="L277" s="30"/>
-      <c r="M277" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N277" s="14"/>
+      <c r="M277" s="13">
+        <f>+_xlfn.XLOOKUP(D277&amp;"-"&amp;E277,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N277" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O277" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -20480,10 +24380,13 @@
       </c>
       <c r="K278" s="11"/>
       <c r="L278" s="30"/>
-      <c r="M278" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N278" s="14"/>
+      <c r="M278" s="13">
+        <f>+_xlfn.XLOOKUP(D278&amp;"-"&amp;E278,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N278" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O278" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -20545,10 +24448,13 @@
       </c>
       <c r="K279" s="11"/>
       <c r="L279" s="30"/>
-      <c r="M279" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N279" s="14"/>
+      <c r="M279" s="13">
+        <f>+_xlfn.XLOOKUP(D279&amp;"-"&amp;E279,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N279" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O279" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -20610,10 +24516,13 @@
       </c>
       <c r="K280" s="11"/>
       <c r="L280" s="30"/>
-      <c r="M280" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N280" s="14"/>
+      <c r="M280" s="13">
+        <f>+_xlfn.XLOOKUP(D280&amp;"-"&amp;E280,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N280" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O280" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -20675,10 +24584,13 @@
       </c>
       <c r="K281" s="11"/>
       <c r="L281" s="30"/>
-      <c r="M281" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N281" s="14"/>
+      <c r="M281" s="13">
+        <f>+_xlfn.XLOOKUP(D281&amp;"-"&amp;E281,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N281" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O281" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -20740,10 +24652,13 @@
       </c>
       <c r="K282" s="11"/>
       <c r="L282" s="30"/>
-      <c r="M282" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N282" s="14"/>
+      <c r="M282" s="13">
+        <f>+_xlfn.XLOOKUP(D282&amp;"-"&amp;E282,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N282" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O282" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -20805,10 +24720,13 @@
       </c>
       <c r="K283" s="11"/>
       <c r="L283" s="30"/>
-      <c r="M283" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N283" s="14"/>
+      <c r="M283" s="13">
+        <f>+_xlfn.XLOOKUP(D283&amp;"-"&amp;E283,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N283" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O283" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -20870,10 +24788,13 @@
       </c>
       <c r="K284" s="11"/>
       <c r="L284" s="30"/>
-      <c r="M284" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N284" s="14"/>
+      <c r="M284" s="13">
+        <f>+_xlfn.XLOOKUP(D284&amp;"-"&amp;E284,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N284" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O284" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -20937,10 +24858,12 @@
       <c r="L285" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="M285" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N285" s="14"/>
+      <c r="M285" s="13">
+        <v>270</v>
+      </c>
+      <c r="N285" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O285" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21004,10 +24927,12 @@
       <c r="L286" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="M286" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N286" s="14"/>
+      <c r="M286" s="13">
+        <v>273</v>
+      </c>
+      <c r="N286" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O286" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21071,10 +24996,12 @@
       <c r="L287" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="M287" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N287" s="14"/>
+      <c r="M287" s="13">
+        <v>270</v>
+      </c>
+      <c r="N287" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O287" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21138,10 +25065,12 @@
       <c r="L288" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="M288" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N288" s="14"/>
+      <c r="M288" s="13">
+        <v>267</v>
+      </c>
+      <c r="N288" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O288" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21205,10 +25134,12 @@
       <c r="L289" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="M289" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N289" s="14"/>
+      <c r="M289" s="13">
+        <v>265</v>
+      </c>
+      <c r="N289" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O289" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21272,10 +25203,12 @@
       <c r="L290" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="M290" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N290" s="14"/>
+      <c r="M290" s="13">
+        <v>256</v>
+      </c>
+      <c r="N290" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O290" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21337,10 +25270,13 @@
       </c>
       <c r="K291" s="11"/>
       <c r="L291" s="30"/>
-      <c r="M291" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N291" s="14"/>
+      <c r="M291" s="13">
+        <f>+_xlfn.XLOOKUP(D291&amp;"-"&amp;E291,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N291" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O291" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21402,10 +25338,13 @@
       </c>
       <c r="K292" s="11"/>
       <c r="L292" s="30"/>
-      <c r="M292" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N292" s="14"/>
+      <c r="M292" s="13">
+        <f>+_xlfn.XLOOKUP(D292&amp;"-"&amp;E292,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N292" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O292" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21467,10 +25406,13 @@
       </c>
       <c r="K293" s="11"/>
       <c r="L293" s="30"/>
-      <c r="M293" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N293" s="14"/>
+      <c r="M293" s="13">
+        <f>+_xlfn.XLOOKUP(D293&amp;"-"&amp;E293,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N293" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O293" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21532,10 +25474,13 @@
       </c>
       <c r="K294" s="11"/>
       <c r="L294" s="30"/>
-      <c r="M294" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N294" s="14"/>
+      <c r="M294" s="13">
+        <f>+_xlfn.XLOOKUP(D294&amp;"-"&amp;E294,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N294" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O294" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21597,10 +25542,13 @@
       </c>
       <c r="K295" s="11"/>
       <c r="L295" s="30"/>
-      <c r="M295" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N295" s="14"/>
+      <c r="M295" s="13">
+        <f>+_xlfn.XLOOKUP(D295&amp;"-"&amp;E295,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N295" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O295" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21662,10 +25610,13 @@
       </c>
       <c r="K296" s="11"/>
       <c r="L296" s="30"/>
-      <c r="M296" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N296" s="14"/>
+      <c r="M296" s="13">
+        <f>+_xlfn.XLOOKUP(D296&amp;"-"&amp;E296,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N296" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O296" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21727,10 +25678,13 @@
       </c>
       <c r="K297" s="11"/>
       <c r="L297" s="30"/>
-      <c r="M297" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N297" s="14"/>
+      <c r="M297" s="13">
+        <f>+_xlfn.XLOOKUP(D297&amp;"-"&amp;E297,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N297" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O297" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21792,10 +25746,13 @@
       </c>
       <c r="K298" s="11"/>
       <c r="L298" s="30"/>
-      <c r="M298" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N298" s="14"/>
+      <c r="M298" s="13">
+        <f>+_xlfn.XLOOKUP(D298&amp;"-"&amp;E298,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N298" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O298" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21859,10 +25816,13 @@
         <v>165</v>
       </c>
       <c r="L299" s="30"/>
-      <c r="M299" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N299" s="14"/>
+      <c r="M299" s="13">
+        <f>+_xlfn.XLOOKUP(D299&amp;"-"&amp;E299,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N299" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O299" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21924,10 +25884,13 @@
       </c>
       <c r="K300" s="11"/>
       <c r="L300" s="30"/>
-      <c r="M300" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N300" s="14"/>
+      <c r="M300" s="13">
+        <f>+_xlfn.XLOOKUP(D300&amp;"-"&amp;E300,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N300" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O300" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -21989,10 +25952,13 @@
       </c>
       <c r="K301" s="11"/>
       <c r="L301" s="30"/>
-      <c r="M301" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N301" s="14"/>
+      <c r="M301" s="13">
+        <f>+_xlfn.XLOOKUP(D301&amp;"-"&amp;E301,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N301" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O301" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -22054,10 +26020,13 @@
       </c>
       <c r="K302" s="11"/>
       <c r="L302" s="30"/>
-      <c r="M302" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N302" s="14"/>
+      <c r="M302" s="13">
+        <f>+_xlfn.XLOOKUP(D302&amp;"-"&amp;E302,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N302" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O302" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -22119,10 +26088,13 @@
       </c>
       <c r="K303" s="11"/>
       <c r="L303" s="30"/>
-      <c r="M303" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N303" s="14"/>
+      <c r="M303" s="13">
+        <f>+_xlfn.XLOOKUP(D303&amp;"-"&amp;E303,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>233.98</v>
+      </c>
+      <c r="N303" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O303" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -22184,10 +26156,13 @@
       </c>
       <c r="K304" s="11"/>
       <c r="L304" s="30"/>
-      <c r="M304" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N304" s="14"/>
+      <c r="M304" s="13">
+        <f>+_xlfn.XLOOKUP(D304&amp;"-"&amp;E304,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>229.5</v>
+      </c>
+      <c r="N304" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O304" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -22249,10 +26224,13 @@
       </c>
       <c r="K305" s="11"/>
       <c r="L305" s="30"/>
-      <c r="M305" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N305" s="14"/>
+      <c r="M305" s="13">
+        <f>+_xlfn.XLOOKUP(D305&amp;"-"&amp;E305,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N305" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O305" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -22314,10 +26292,13 @@
       </c>
       <c r="K306" s="11"/>
       <c r="L306" s="30"/>
-      <c r="M306" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N306" s="14"/>
+      <c r="M306" s="13">
+        <f>+_xlfn.XLOOKUP(D306&amp;"-"&amp;E306,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N306" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O306" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -22379,10 +26360,13 @@
       </c>
       <c r="K307" s="11"/>
       <c r="L307" s="30"/>
-      <c r="M307" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N307" s="14"/>
+      <c r="M307" s="13">
+        <f>+_xlfn.XLOOKUP(D307&amp;"-"&amp;E307,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N307" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O307" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -22444,10 +26428,13 @@
       </c>
       <c r="K308" s="11"/>
       <c r="L308" s="30"/>
-      <c r="M308" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N308" s="14"/>
+      <c r="M308" s="13">
+        <f>+_xlfn.XLOOKUP(D308&amp;"-"&amp;E308,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N308" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O308" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -22509,10 +26496,13 @@
       </c>
       <c r="K309" s="11"/>
       <c r="L309" s="30"/>
-      <c r="M309" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N309" s="14"/>
+      <c r="M309" s="13">
+        <f>+_xlfn.XLOOKUP(D309&amp;"-"&amp;E309,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N309" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O309" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -22574,10 +26564,13 @@
       </c>
       <c r="K310" s="11"/>
       <c r="L310" s="30"/>
-      <c r="M310" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N310" s="14"/>
+      <c r="M310" s="13">
+        <f>+_xlfn.XLOOKUP(D310&amp;"-"&amp;E310,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N310" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O310" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -22639,10 +26632,13 @@
       </c>
       <c r="K311" s="11"/>
       <c r="L311" s="30"/>
-      <c r="M311" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N311" s="14"/>
+      <c r="M311" s="13">
+        <f>+_xlfn.XLOOKUP(D311&amp;"-"&amp;E311,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N311" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O311" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -22704,10 +26700,12 @@
       </c>
       <c r="K312" s="11"/>
       <c r="L312" s="30"/>
-      <c r="M312" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N312" s="14"/>
+      <c r="M312" s="13">
+        <v>290</v>
+      </c>
+      <c r="N312" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O312" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -22769,10 +26767,12 @@
       </c>
       <c r="K313" s="11"/>
       <c r="L313" s="30"/>
-      <c r="M313" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N313" s="14"/>
+      <c r="M313" s="13">
+        <v>294</v>
+      </c>
+      <c r="N313" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O313" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -22834,10 +26834,12 @@
       </c>
       <c r="K314" s="11"/>
       <c r="L314" s="30"/>
-      <c r="M314" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N314" s="14"/>
+      <c r="M314" s="13">
+        <v>291</v>
+      </c>
+      <c r="N314" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O314" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -22899,10 +26901,12 @@
       </c>
       <c r="K315" s="11"/>
       <c r="L315" s="30"/>
-      <c r="M315" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N315" s="14"/>
+      <c r="M315" s="13">
+        <v>288</v>
+      </c>
+      <c r="N315" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O315" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -22964,10 +26968,12 @@
       </c>
       <c r="K316" s="11"/>
       <c r="L316" s="30"/>
-      <c r="M316" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N316" s="14"/>
+      <c r="M316" s="13">
+        <v>285</v>
+      </c>
+      <c r="N316" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O316" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -23029,10 +27035,12 @@
       </c>
       <c r="K317" s="11"/>
       <c r="L317" s="30"/>
-      <c r="M317" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N317" s="14"/>
+      <c r="M317" s="13">
+        <v>277</v>
+      </c>
+      <c r="N317" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O317" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -23094,10 +27102,13 @@
       </c>
       <c r="K318" s="11"/>
       <c r="L318" s="30"/>
-      <c r="M318" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N318" s="14"/>
+      <c r="M318" s="13">
+        <f>+_xlfn.XLOOKUP(D318&amp;"-"&amp;E318,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N318" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O318" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -23159,10 +27170,13 @@
       </c>
       <c r="K319" s="11"/>
       <c r="L319" s="30"/>
-      <c r="M319" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N319" s="14"/>
+      <c r="M319" s="13">
+        <f>+_xlfn.XLOOKUP(D319&amp;"-"&amp;E319,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N319" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O319" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -23224,10 +27238,13 @@
       </c>
       <c r="K320" s="11"/>
       <c r="L320" s="30"/>
-      <c r="M320" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N320" s="14"/>
+      <c r="M320" s="13">
+        <f>+_xlfn.XLOOKUP(D320&amp;"-"&amp;E320,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N320" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O320" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -23289,10 +27306,13 @@
       </c>
       <c r="K321" s="11"/>
       <c r="L321" s="30"/>
-      <c r="M321" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N321" s="14"/>
+      <c r="M321" s="13">
+        <f>+_xlfn.XLOOKUP(D321&amp;"-"&amp;E321,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N321" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O321" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -23354,10 +27374,13 @@
       </c>
       <c r="K322" s="11"/>
       <c r="L322" s="30"/>
-      <c r="M322" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N322" s="14"/>
+      <c r="M322" s="13">
+        <f>+_xlfn.XLOOKUP(D322&amp;"-"&amp;E322,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N322" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O322" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -23419,10 +27442,13 @@
       </c>
       <c r="K323" s="11"/>
       <c r="L323" s="30"/>
-      <c r="M323" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N323" s="14"/>
+      <c r="M323" s="13">
+        <f>+_xlfn.XLOOKUP(D323&amp;"-"&amp;E323,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N323" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O323" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -23484,10 +27510,13 @@
       </c>
       <c r="K324" s="11"/>
       <c r="L324" s="30"/>
-      <c r="M324" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N324" s="14"/>
+      <c r="M324" s="13">
+        <f>+_xlfn.XLOOKUP(D324&amp;"-"&amp;E324,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N324" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O324" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -23549,10 +27578,13 @@
       </c>
       <c r="K325" s="11"/>
       <c r="L325" s="30"/>
-      <c r="M325" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N325" s="14"/>
+      <c r="M325" s="13">
+        <f>+_xlfn.XLOOKUP(D325&amp;"-"&amp;E325,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N325" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O325" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -23616,10 +27648,13 @@
         <v>194</v>
       </c>
       <c r="L326" s="30"/>
-      <c r="M326" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N326" s="14"/>
+      <c r="M326" s="13">
+        <f>+_xlfn.XLOOKUP(D326&amp;"-"&amp;E326,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>283</v>
+      </c>
+      <c r="N326" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O326" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -23681,10 +27716,13 @@
       </c>
       <c r="K327" s="11"/>
       <c r="L327" s="30"/>
-      <c r="M327" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N327" s="14"/>
+      <c r="M327" s="13">
+        <f>+_xlfn.XLOOKUP(D327&amp;"-"&amp;E327,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>280.5</v>
+      </c>
+      <c r="N327" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O327" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -23746,10 +27784,13 @@
       </c>
       <c r="K328" s="11"/>
       <c r="L328" s="30"/>
-      <c r="M328" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N328" s="14"/>
+      <c r="M328" s="13">
+        <f>+_xlfn.XLOOKUP(D328&amp;"-"&amp;E328,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>278</v>
+      </c>
+      <c r="N328" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O328" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -23811,10 +27852,13 @@
       </c>
       <c r="K329" s="11"/>
       <c r="L329" s="30"/>
-      <c r="M329" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N329" s="14"/>
+      <c r="M329" s="13">
+        <f>+_xlfn.XLOOKUP(D329&amp;"-"&amp;E329,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>275</v>
+      </c>
+      <c r="N329" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O329" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -23876,10 +27920,13 @@
       </c>
       <c r="K330" s="11"/>
       <c r="L330" s="30"/>
-      <c r="M330" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N330" s="14"/>
+      <c r="M330" s="13">
+        <f>+_xlfn.XLOOKUP(D330&amp;"-"&amp;E330,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>266</v>
+      </c>
+      <c r="N330" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O330" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -23941,10 +27988,13 @@
       </c>
       <c r="K331" s="11"/>
       <c r="L331" s="30"/>
-      <c r="M331" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N331" s="14"/>
+      <c r="M331" s="13">
+        <f>+_xlfn.XLOOKUP(D331&amp;"-"&amp;E331,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N331" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O331" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24006,10 +28056,13 @@
       </c>
       <c r="K332" s="11"/>
       <c r="L332" s="30"/>
-      <c r="M332" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N332" s="14"/>
+      <c r="M332" s="13">
+        <f>+_xlfn.XLOOKUP(D332&amp;"-"&amp;E332,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N332" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O332" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24071,10 +28124,13 @@
       </c>
       <c r="K333" s="11"/>
       <c r="L333" s="30"/>
-      <c r="M333" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N333" s="14"/>
+      <c r="M333" s="13">
+        <f>+_xlfn.XLOOKUP(D333&amp;"-"&amp;E333,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N333" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O333" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24136,10 +28192,13 @@
       </c>
       <c r="K334" s="11"/>
       <c r="L334" s="30"/>
-      <c r="M334" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N334" s="14"/>
+      <c r="M334" s="13">
+        <f>+_xlfn.XLOOKUP(D334&amp;"-"&amp;E334,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N334" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O334" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24201,10 +28260,13 @@
       </c>
       <c r="K335" s="11"/>
       <c r="L335" s="30"/>
-      <c r="M335" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N335" s="14"/>
+      <c r="M335" s="13">
+        <f>+_xlfn.XLOOKUP(D335&amp;"-"&amp;E335,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N335" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O335" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24266,10 +28328,13 @@
       </c>
       <c r="K336" s="11"/>
       <c r="L336" s="30"/>
-      <c r="M336" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N336" s="14"/>
+      <c r="M336" s="13">
+        <f>+_xlfn.XLOOKUP(D336&amp;"-"&amp;E336,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N336" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O336" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24331,10 +28396,13 @@
       </c>
       <c r="K337" s="11"/>
       <c r="L337" s="30"/>
-      <c r="M337" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N337" s="14"/>
+      <c r="M337" s="13">
+        <f>+_xlfn.XLOOKUP(D337&amp;"-"&amp;E337,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N337" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O337" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24396,10 +28464,13 @@
       </c>
       <c r="K338" s="11"/>
       <c r="L338" s="30"/>
-      <c r="M338" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N338" s="14"/>
+      <c r="M338" s="13">
+        <f>+_xlfn.XLOOKUP(D338&amp;"-"&amp;E338,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N338" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O338" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24461,10 +28532,13 @@
       </c>
       <c r="K339" s="11"/>
       <c r="L339" s="30"/>
-      <c r="M339" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N339" s="14"/>
+      <c r="M339" s="13">
+        <f>+_xlfn.XLOOKUP(D339&amp;"-"&amp;E339,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N339" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O339" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24526,10 +28600,13 @@
       </c>
       <c r="K340" s="11"/>
       <c r="L340" s="30"/>
-      <c r="M340" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N340" s="14"/>
+      <c r="M340" s="13">
+        <f>+_xlfn.XLOOKUP(D340&amp;"-"&amp;E340,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N340" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O340" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24591,10 +28668,13 @@
       </c>
       <c r="K341" s="11"/>
       <c r="L341" s="30"/>
-      <c r="M341" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N341" s="14"/>
+      <c r="M341" s="13">
+        <f>+_xlfn.XLOOKUP(D341&amp;"-"&amp;E341,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>226.59</v>
+      </c>
+      <c r="N341" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O341" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24656,10 +28736,13 @@
       </c>
       <c r="K342" s="11"/>
       <c r="L342" s="30"/>
-      <c r="M342" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N342" s="14"/>
+      <c r="M342" s="13">
+        <f>+_xlfn.XLOOKUP(D342&amp;"-"&amp;E342,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>230.83</v>
+      </c>
+      <c r="N342" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O342" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24721,10 +28804,13 @@
       </c>
       <c r="K343" s="11"/>
       <c r="L343" s="30"/>
-      <c r="M343" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N343" s="14"/>
+      <c r="M343" s="13">
+        <f>+_xlfn.XLOOKUP(D343&amp;"-"&amp;E343,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>230.88</v>
+      </c>
+      <c r="N343" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O343" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24786,10 +28872,13 @@
       </c>
       <c r="K344" s="11"/>
       <c r="L344" s="30"/>
-      <c r="M344" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N344" s="14"/>
+      <c r="M344" s="13">
+        <f>+_xlfn.XLOOKUP(D344&amp;"-"&amp;E344,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>230.88</v>
+      </c>
+      <c r="N344" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O344" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24851,10 +28940,13 @@
       </c>
       <c r="K345" s="11"/>
       <c r="L345" s="30"/>
-      <c r="M345" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N345" s="14"/>
+      <c r="M345" s="13">
+        <f>+_xlfn.XLOOKUP(D345&amp;"-"&amp;E345,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>230.93</v>
+      </c>
+      <c r="N345" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O345" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24916,10 +29008,13 @@
       </c>
       <c r="K346" s="11"/>
       <c r="L346" s="30"/>
-      <c r="M346" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N346" s="14"/>
+      <c r="M346" s="13">
+        <f>+_xlfn.XLOOKUP(D346&amp;"-"&amp;E346,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>226.48</v>
+      </c>
+      <c r="N346" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O346" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -24981,10 +29076,13 @@
       </c>
       <c r="K347" s="11"/>
       <c r="L347" s="30"/>
-      <c r="M347" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N347" s="14"/>
+      <c r="M347" s="13">
+        <f>+_xlfn.XLOOKUP(D347&amp;"-"&amp;E347,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N347" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O347" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -25046,10 +29144,13 @@
       </c>
       <c r="K348" s="11"/>
       <c r="L348" s="30"/>
-      <c r="M348" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N348" s="14"/>
+      <c r="M348" s="13">
+        <f>+_xlfn.XLOOKUP(D348&amp;"-"&amp;E348,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N348" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O348" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -25111,10 +29212,13 @@
       </c>
       <c r="K349" s="11"/>
       <c r="L349" s="30"/>
-      <c r="M349" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N349" s="14"/>
+      <c r="M349" s="13">
+        <f>+_xlfn.XLOOKUP(D349&amp;"-"&amp;E349,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N349" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O349" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -25176,10 +29280,13 @@
       </c>
       <c r="K350" s="11"/>
       <c r="L350" s="30"/>
-      <c r="M350" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N350" s="14"/>
+      <c r="M350" s="13">
+        <f>+_xlfn.XLOOKUP(D350&amp;"-"&amp;E350,'[1]Listado Lotes'!$K$3:$K$385,'[1]Listado Lotes'!$E$3:$E$385)</f>
+        <v>298.69</v>
+      </c>
+      <c r="N350" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O350" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -25241,10 +29348,12 @@
       </c>
       <c r="K351" s="11"/>
       <c r="L351" s="30"/>
-      <c r="M351" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N351" s="14"/>
+      <c r="M351" s="13">
+        <v>298</v>
+      </c>
+      <c r="N351" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O351" s="14" t="e">
         <v>#N/A</v>
       </c>
@@ -25306,10 +29415,12 @@
       </c>
       <c r="K352" s="11"/>
       <c r="L352" s="30"/>
-      <c r="M352" s="13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N352" s="14"/>
+      <c r="M352" s="13">
+        <v>299</v>
+      </c>
+      <c r="N352" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="O352" s="14" t="e">
         <v>#N/A</v>
       </c>
